--- a/output/screener_output.xlsx
+++ b/output/screener_output.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W20"/>
+  <dimension ref="A1:W28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -550,75 +550,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>20.53</v>
+        <v>30.34</v>
       </c>
       <c r="D2" t="n">
-        <v>24.84</v>
+        <v>58.36</v>
       </c>
       <c r="E2" t="n">
-        <v>32.47</v>
+        <v>15.35</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>141.75</v>
+        <v>5.95</v>
       </c>
       <c r="H2" t="n">
-        <v>1.13</v>
+        <v>0.23</v>
       </c>
       <c r="I2" t="n">
-        <v>1629</v>
+        <v>21786</v>
       </c>
       <c r="J2" t="n">
-        <v>416</v>
+        <v>6768</v>
       </c>
       <c r="K2" t="n">
-        <v>565</v>
+        <v>38</v>
       </c>
       <c r="L2" t="n">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="M2" t="n">
-        <v>83</v>
+        <v>49470</v>
       </c>
       <c r="N2" t="n">
-        <v>1213</v>
+        <v>15018</v>
       </c>
       <c r="O2" t="n">
-        <v>11.44</v>
+        <v>22.7</v>
       </c>
       <c r="P2" t="n">
-        <v>19.94</v>
+        <v>17.86</v>
       </c>
       <c r="Q2" t="n">
-        <v>19.98</v>
+        <v>15.83</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Abbott India Ltd</t>
+          <t xml:space="preserve">Adani Ports &amp; Special Economic Zone Ltd
+</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>46</v>
+        <v>12.9</v>
       </c>
       <c r="T2" t="n">
-        <v>1536236.24</v>
+        <v>675598.01</v>
       </c>
       <c r="U2" t="n">
-        <v>75.58</v>
+        <v>48.9</v>
       </c>
       <c r="V2" t="n">
-        <v>4.48</v>
+        <v>2.31</v>
       </c>
       <c r="W2" t="n">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -627,76 +628,75 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>30.34</v>
+        <v>41.37</v>
       </c>
       <c r="D3" t="n">
-        <v>58.36</v>
+        <v>36.2</v>
       </c>
       <c r="E3" t="n">
-        <v>15.35</v>
+        <v>48.28</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="G3" t="n">
-        <v>5.95</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>0.23</v>
+        <v>0.55</v>
       </c>
       <c r="I3" t="n">
-        <v>21786</v>
+        <v>17651</v>
       </c>
       <c r="J3" t="n">
-        <v>6768</v>
+        <v>3481</v>
       </c>
       <c r="K3" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="L3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>49470</v>
+        <v>34616</v>
       </c>
       <c r="N3" t="n">
-        <v>15018</v>
+        <v>14170</v>
       </c>
       <c r="O3" t="n">
-        <v>18.86</v>
+        <v>20.15</v>
       </c>
       <c r="P3" t="n">
-        <v>16.01</v>
+        <v>77.78</v>
       </c>
       <c r="Q3" t="n">
-        <v>15.48</v>
+        <v>82.12</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adani Ports &amp; Special Economic Zone Ltd
-</t>
+          <t>Adani Power Ltd</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>12.9</v>
+        <v>32.2</v>
       </c>
       <c r="T3" t="n">
-        <v>675598.01</v>
+        <v>1372183.55</v>
       </c>
       <c r="U3" t="n">
-        <v>48.9</v>
+        <v>44.57</v>
       </c>
       <c r="V3" t="n">
-        <v>2.31</v>
+        <v>9.91</v>
       </c>
       <c r="W3" t="n">
-        <v>1.16</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -705,71 +705,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>41.37</v>
+        <v>15.66</v>
       </c>
       <c r="D4" t="n">
-        <v>36.2</v>
+        <v>21.37</v>
       </c>
       <c r="E4" t="n">
-        <v>48.28</v>
+        <v>29.68</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8</v>
+        <v>0.13</v>
       </c>
       <c r="G4" t="n">
-        <v>8.300000000000001</v>
+        <v>41</v>
       </c>
       <c r="H4" t="n">
-        <v>0.55</v>
+        <v>1.19</v>
       </c>
       <c r="I4" t="n">
-        <v>17651</v>
+        <v>8652</v>
       </c>
       <c r="J4" t="n">
-        <v>3481</v>
+        <v>2548</v>
       </c>
       <c r="K4" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="M4" t="n">
-        <v>34616</v>
+        <v>2474</v>
       </c>
       <c r="N4" t="n">
-        <v>14170</v>
+        <v>6104</v>
       </c>
       <c r="O4" t="n">
-        <v>19.12</v>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
+        <v>12.54</v>
+      </c>
+      <c r="P4" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>9.82</v>
+      </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Adani Power Ltd</t>
+          <t>Asian Paints
+Indian Multi-National Paint and Coating Manufacturing Company</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>32.2</v>
+        <v>41.75</v>
       </c>
       <c r="T4" t="n">
-        <v>1372183.55</v>
+        <v>2126725.18</v>
       </c>
       <c r="U4" t="n">
-        <v>44.57</v>
+        <v>73.37</v>
       </c>
       <c r="V4" t="n">
-        <v>9.91</v>
+        <v>3.9</v>
       </c>
       <c r="W4" t="n">
-        <v>1.65</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -778,70 +783,69 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>15.66</v>
+        <v>17.18</v>
       </c>
       <c r="D5" t="n">
-        <v>21.37</v>
+        <v>19.53</v>
       </c>
       <c r="E5" t="n">
-        <v>29.68</v>
+        <v>26.61</v>
       </c>
       <c r="F5" t="n">
-        <v>0.13</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>41</v>
+        <v>174.42</v>
       </c>
       <c r="H5" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="I5" t="n">
-        <v>8652</v>
+        <v>6630</v>
       </c>
       <c r="J5" t="n">
-        <v>2548</v>
+        <v>72</v>
       </c>
       <c r="K5" t="n">
-        <v>57</v>
+        <v>276</v>
       </c>
       <c r="L5" t="n">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="M5" t="n">
-        <v>2474</v>
+        <v>1912</v>
       </c>
       <c r="N5" t="n">
-        <v>6104</v>
+        <v>6558</v>
       </c>
       <c r="O5" t="n">
-        <v>10.51</v>
+        <v>15.22</v>
       </c>
       <c r="P5" t="n">
-        <v>12.23</v>
+        <v>10.99</v>
       </c>
       <c r="Q5" t="n">
-        <v>12.25</v>
+        <v>11.86</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Asian Paints
-Indian Multi-National Paint and Coating Manufacturing Company</t>
+          <t>Bajaj Auto Ltd</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>41.75</v>
+        <v>33.5</v>
       </c>
       <c r="T5" t="n">
-        <v>2126725.18</v>
+        <v>653817.3</v>
       </c>
       <c r="U5" t="n">
-        <v>73.37</v>
+        <v>29.91</v>
       </c>
       <c r="V5" t="n">
-        <v>3.9</v>
+        <v>9.83</v>
       </c>
       <c r="W5" t="n">
-        <v>2.42</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="6">
@@ -892,13 +896,13 @@
         <v>4659</v>
       </c>
       <c r="O6" t="n">
-        <v>10.84</v>
+        <v>11.2</v>
       </c>
       <c r="P6" t="n">
-        <v>14.32</v>
+        <v>21.26</v>
       </c>
       <c r="Q6" t="n">
-        <v>16.1</v>
+        <v>18.92</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -924,7 +928,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>BOSCHLTD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -933,76 +937,75 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.12</v>
+        <v>14.89</v>
       </c>
       <c r="D7" t="n">
-        <v>75.59</v>
+        <v>12.52</v>
       </c>
       <c r="E7" t="n">
-        <v>15.55</v>
+        <v>20.64</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>35.34</v>
+        <v>71.78</v>
       </c>
       <c r="H7" t="n">
-        <v>0.79</v>
+        <v>0.96</v>
       </c>
       <c r="I7" t="n">
-        <v>7116</v>
+        <v>1536</v>
       </c>
       <c r="J7" t="n">
-        <v>2982</v>
+        <v>283</v>
       </c>
       <c r="K7" t="n">
-        <v>51</v>
+        <v>844</v>
       </c>
       <c r="L7" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="M7" t="n">
-        <v>559</v>
+        <v>39</v>
       </c>
       <c r="N7" t="n">
-        <v>4134</v>
+        <v>1253</v>
       </c>
       <c r="O7" t="n">
-        <v>10.35</v>
+        <v>15.26</v>
       </c>
       <c r="P7" t="n">
-        <v>10.26</v>
+        <v>44.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>10.36</v>
+        <v>44.09</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cipla Ltd
-</t>
+          <t>Bosch Ltd</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>22.8</v>
+        <v>20.6</v>
       </c>
       <c r="T7" t="n">
-        <v>439803.15</v>
+        <v>2599556.05</v>
       </c>
       <c r="U7" t="n">
-        <v>59.75</v>
+        <v>58.43</v>
       </c>
       <c r="V7" t="n">
-        <v>5.93</v>
+        <v>6.47</v>
       </c>
       <c r="W7" t="n">
-        <v>0.12</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>BPCL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1011,75 +1014,75 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9.369999999999999</v>
+        <v>5.99</v>
       </c>
       <c r="D8" t="n">
-        <v>87.42</v>
+        <v>9.84</v>
       </c>
       <c r="E8" t="n">
-        <v>15.72</v>
+        <v>35.51</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="G8" t="n">
-        <v>160.03</v>
+        <v>11.36</v>
       </c>
       <c r="H8" t="n">
-        <v>0.32</v>
+        <v>2.21</v>
       </c>
       <c r="I8" t="n">
-        <v>4328</v>
+        <v>46457</v>
       </c>
       <c r="J8" t="n">
-        <v>1921</v>
+        <v>10521</v>
       </c>
       <c r="K8" t="n">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="L8" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="M8" t="n">
-        <v>35</v>
+        <v>54599</v>
       </c>
       <c r="N8" t="n">
-        <v>2407</v>
+        <v>35936</v>
       </c>
       <c r="O8" t="n">
-        <v>15.79</v>
+        <v>17.96</v>
       </c>
       <c r="P8" t="n">
-        <v>17.79</v>
+        <v>-5.63</v>
       </c>
       <c r="Q8" t="n">
-        <v>16.69</v>
+        <v>-3.56</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>ICICI Lombard General Insurance Company Ltd</t>
+          <t>Bharat Petroleum Corporation Ltd</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>22.5</v>
+        <v>32.1</v>
       </c>
       <c r="T8" t="n">
-        <v>1271789.21</v>
+        <v>468662.13</v>
       </c>
       <c r="U8" t="n">
-        <v>49</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>7.86</v>
+        <v>0.72</v>
       </c>
       <c r="W8" t="n">
-        <v>3.46</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1088,75 +1091,75 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11.85</v>
+        <v>26.26</v>
       </c>
       <c r="D9" t="n">
-        <v>76.3</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>892.5700000000001</v>
+        <v>45.17</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="G9" t="n">
-        <v>22.61</v>
+        <v>11.24</v>
       </c>
       <c r="H9" t="n">
-        <v>56.39</v>
+        <v>0.6</v>
       </c>
       <c r="I9" t="n">
-        <v>32942</v>
+        <v>22589</v>
       </c>
       <c r="J9" t="n">
-        <v>11759</v>
+        <v>4486</v>
       </c>
       <c r="K9" t="n">
-        <v>212</v>
+        <v>61</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M9" t="n">
-        <v>17</v>
+        <v>6523</v>
       </c>
       <c r="N9" t="n">
-        <v>21183</v>
+        <v>18103</v>
       </c>
       <c r="O9" t="n">
-        <v>19.3</v>
+        <v>11.74</v>
       </c>
       <c r="P9" t="n">
-        <v>18.57</v>
+        <v>28.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>-34.6</v>
+        <v>27.79</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Interglobe Aviation Ltd</t>
+          <t>Coal India Ltd</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>24.5</v>
+        <v>63.6</v>
       </c>
       <c r="T9" t="n">
-        <v>1040632.92</v>
+        <v>454024.84</v>
       </c>
       <c r="U9" t="n">
-        <v>76.23</v>
+        <v>34.27</v>
       </c>
       <c r="V9" t="n">
-        <v>7.87</v>
+        <v>14.75</v>
       </c>
       <c r="W9" t="n">
-        <v>4.27</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1165,75 +1168,75 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.08</v>
+        <v>19.91</v>
       </c>
       <c r="D10" t="n">
-        <v>23.7</v>
+        <v>28.32</v>
       </c>
       <c r="E10" t="n">
-        <v>29.79</v>
+        <v>19.74</v>
       </c>
       <c r="F10" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G10" t="n">
+        <v>51.71</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="I10" t="n">
+        <v>8577</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4034</v>
+      </c>
+      <c r="K10" t="n">
+        <v>67</v>
+      </c>
+      <c r="L10" t="n">
+        <v>12</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2002</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4543</v>
+      </c>
+      <c r="O10" t="n">
+        <v>13.16</v>
+      </c>
+      <c r="P10" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>29.16</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Dr Reddys Laboratories Ltd</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2441803.28</v>
+      </c>
+      <c r="U10" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="V10" t="n">
+        <v>10.19</v>
+      </c>
+      <c r="W10" t="n">
         <v>0.09</v>
-      </c>
-      <c r="G10" t="n">
-        <v>87.52</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="I10" t="n">
-        <v>30303</v>
-      </c>
-      <c r="J10" t="n">
-        <v>5093</v>
-      </c>
-      <c r="K10" t="n">
-        <v>63</v>
-      </c>
-      <c r="L10" t="n">
-        <v>73</v>
-      </c>
-      <c r="M10" t="n">
-        <v>8359</v>
-      </c>
-      <c r="N10" t="n">
-        <v>25210</v>
-      </c>
-      <c r="O10" t="n">
-        <v>12.16</v>
-      </c>
-      <c r="P10" t="n">
-        <v>9.390000000000001</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>10.15</v>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>Infosys Ltd</t>
-        </is>
-      </c>
-      <c r="S10" t="n">
-        <v>40</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1112279.92</v>
-      </c>
-      <c r="U10" t="n">
-        <v>35.99</v>
-      </c>
-      <c r="V10" t="n">
-        <v>8.970000000000001</v>
-      </c>
-      <c r="W10" t="n">
-        <v>4.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1242,75 +1245,75 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>26.02</v>
+        <v>24.2</v>
       </c>
       <c r="D11" t="n">
-        <v>34.33</v>
+        <v>26.18</v>
       </c>
       <c r="E11" t="n">
-        <v>34.4</v>
+        <v>22.17</v>
       </c>
       <c r="F11" t="n">
         <v>0.02</v>
       </c>
       <c r="G11" t="n">
-        <v>82.73999999999999</v>
+        <v>114.71</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="I11" t="n">
-        <v>1097</v>
+        <v>6558</v>
       </c>
       <c r="J11" t="n">
-        <v>215</v>
+        <v>2834</v>
       </c>
       <c r="K11" t="n">
-        <v>14</v>
+        <v>146</v>
       </c>
       <c r="L11" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="M11" t="n">
-        <v>60</v>
+        <v>419</v>
       </c>
       <c r="N11" t="n">
-        <v>882</v>
+        <v>3724</v>
       </c>
       <c r="O11" t="n">
-        <v>15.45</v>
+        <v>18.32</v>
       </c>
       <c r="P11" t="n">
-        <v>24.79</v>
+        <v>33.42</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.44</v>
+        <v>33.58</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Indian Railway Catering &amp; Tourism Corporation Ltd</t>
+          <t>Eicher Motors Ltd</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>53.8</v>
+        <v>31.1</v>
       </c>
       <c r="T11" t="n">
-        <v>1258520.29</v>
+        <v>222391.83</v>
       </c>
       <c r="U11" t="n">
-        <v>60.44</v>
+        <v>15.62</v>
       </c>
       <c r="V11" t="n">
-        <v>5.74</v>
+        <v>13.61</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>HAVELLS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1319,152 +1322,152 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7.03</v>
+        <v>6.84</v>
       </c>
       <c r="D12" t="n">
-        <v>13.51</v>
+        <v>10.12</v>
       </c>
       <c r="E12" t="n">
-        <v>77.67</v>
+        <v>17.07</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="G12" t="n">
-        <v>3.54</v>
+        <v>25.36</v>
       </c>
       <c r="H12" t="n">
-        <v>8.029999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="I12" t="n">
-        <v>20445</v>
+        <v>3571</v>
       </c>
       <c r="J12" t="n">
-        <v>2179</v>
+        <v>1618</v>
       </c>
       <c r="K12" t="n">
-        <v>95</v>
+        <v>20</v>
       </c>
       <c r="L12" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="M12" t="n">
-        <v>2071</v>
+        <v>303</v>
       </c>
       <c r="N12" t="n">
-        <v>18266</v>
+        <v>1953</v>
       </c>
       <c r="O12" t="n">
-        <v>10.21</v>
+        <v>18.58</v>
       </c>
       <c r="P12" t="n">
-        <v>9.75</v>
+        <v>7.61</v>
       </c>
       <c r="Q12" t="n">
-        <v>8.210000000000001</v>
+        <v>6.66</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Larsen &amp; Toubro Ltd</t>
+          <t>Havells India Ltd</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>17.18</v>
+        <v>24.4</v>
       </c>
       <c r="T12" t="n">
-        <v>1124597.5</v>
+        <v>2521508.87</v>
       </c>
       <c r="U12" t="n">
-        <v>30.8</v>
+        <v>45.41</v>
       </c>
       <c r="V12" t="n">
-        <v>2.48</v>
+        <v>14.08</v>
       </c>
       <c r="W12" t="n">
-        <v>1.26</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LTIM</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>Jun 2015</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>12.91</v>
+        <v>20</v>
       </c>
       <c r="D13" t="n">
-        <v>17.98</v>
+        <v>23.12</v>
       </c>
       <c r="E13" t="n">
-        <v>22.9</v>
+        <v>30.31</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="G13" t="n">
-        <v>31.93</v>
+        <v>105.63</v>
       </c>
       <c r="H13" t="n">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>9588</v>
+        <v>7627</v>
       </c>
       <c r="J13" t="n">
-        <v>3918</v>
+        <v>2088</v>
       </c>
       <c r="K13" t="n">
-        <v>155</v>
+        <v>26</v>
       </c>
       <c r="L13" t="n">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="M13" t="n">
-        <v>2071</v>
+        <v>648</v>
       </c>
       <c r="N13" t="n">
-        <v>5670</v>
+        <v>5539</v>
       </c>
       <c r="O13" t="n">
-        <v>20.78</v>
+        <v>38.72</v>
       </c>
       <c r="P13" t="n">
-        <v>19.09</v>
+        <v>32.15</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.01</v>
+        <v>33.22</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>LTIMindtree Ltd</t>
+          <t>HCL Technologies Ltd</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>34.1</v>
+        <v>29.6</v>
       </c>
       <c r="T13" t="n">
-        <v>1347046.9</v>
+        <v>412593.29</v>
       </c>
       <c r="U13" t="n">
-        <v>64.52</v>
+        <v>63.63</v>
       </c>
       <c r="V13" t="n">
-        <v>2.38</v>
+        <v>5.44</v>
       </c>
       <c r="W13" t="n">
-        <v>4.43</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>ICICIGI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1473,75 +1476,75 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9.51</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>13.13</v>
+        <v>87.42</v>
       </c>
       <c r="E14" t="n">
-        <v>15.75</v>
+        <v>15.72</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>117.91</v>
+        <v>160.03</v>
       </c>
       <c r="H14" t="n">
-        <v>1.23</v>
+        <v>0.32</v>
       </c>
       <c r="I14" t="n">
-        <v>28666</v>
+        <v>4328</v>
       </c>
       <c r="J14" t="n">
-        <v>11865</v>
+        <v>1921</v>
       </c>
       <c r="K14" t="n">
-        <v>429</v>
+        <v>39</v>
       </c>
       <c r="L14" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M14" t="n">
-        <v>119</v>
+        <v>35</v>
       </c>
       <c r="N14" t="n">
-        <v>16801</v>
+        <v>2407</v>
       </c>
       <c r="O14" t="n">
-        <v>10.4</v>
+        <v>17.65</v>
       </c>
       <c r="P14" t="n">
-        <v>15.57</v>
+        <v>14.34</v>
       </c>
       <c r="Q14" t="n">
-        <v>15.16</v>
+        <v>12.36</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>Maruti Suzuki India Ltd</t>
+          <t>ICICI Lombard General Insurance Company Ltd</t>
         </is>
       </c>
       <c r="S14" t="n">
-        <v>23.67</v>
+        <v>22.5</v>
       </c>
       <c r="T14" t="n">
-        <v>1503863.63</v>
+        <v>1271789.21</v>
       </c>
       <c r="U14" t="n">
-        <v>20.78</v>
+        <v>49</v>
       </c>
       <c r="V14" t="n">
-        <v>8.26</v>
+        <v>7.86</v>
       </c>
       <c r="W14" t="n">
-        <v>1.78</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1550,75 +1553,71 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>9.66</v>
+        <v>11.85</v>
       </c>
       <c r="D15" t="n">
-        <v>17.39</v>
+        <v>76.3</v>
       </c>
       <c r="E15" t="n">
-        <v>16.94</v>
+        <v>892.5700000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>0.45</v>
+        <v>0.02</v>
       </c>
       <c r="G15" t="n">
-        <v>11.36</v>
+        <v>22.61</v>
       </c>
       <c r="H15" t="n">
-        <v>0.83</v>
+        <v>56.39</v>
       </c>
       <c r="I15" t="n">
-        <v>156466</v>
+        <v>32942</v>
       </c>
       <c r="J15" t="n">
-        <v>57203</v>
+        <v>11759</v>
       </c>
       <c r="K15" t="n">
-        <v>39</v>
+        <v>212</v>
       </c>
       <c r="L15" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>153181</v>
+        <v>17</v>
       </c>
       <c r="N15" t="n">
-        <v>99263</v>
+        <v>21183</v>
       </c>
       <c r="O15" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="P15" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>4.71</v>
-      </c>
+        <v>51.18</v>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Oil &amp; Natural Gas Corpn Ltd</t>
+          <t>Interglobe Aviation Ltd</t>
         </is>
       </c>
       <c r="S15" t="n">
-        <v>19.71</v>
+        <v>24.5</v>
       </c>
       <c r="T15" t="n">
-        <v>390111.05</v>
+        <v>1040632.92</v>
       </c>
       <c r="U15" t="n">
-        <v>18.15</v>
+        <v>76.23</v>
       </c>
       <c r="V15" t="n">
-        <v>10.36</v>
+        <v>7.87</v>
       </c>
       <c r="W15" t="n">
-        <v>1.11</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1627,75 +1626,75 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>14.11</v>
+        <v>17.08</v>
       </c>
       <c r="D16" t="n">
-        <v>21.87</v>
+        <v>23.7</v>
       </c>
       <c r="E16" t="n">
-        <v>20.78</v>
+        <v>29.79</v>
       </c>
       <c r="F16" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="G16" t="n">
-        <v>54.33</v>
+        <v>87.52</v>
       </c>
       <c r="H16" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="I16" t="n">
-        <v>4493</v>
+        <v>30303</v>
       </c>
       <c r="J16" t="n">
-        <v>1769</v>
+        <v>5093</v>
       </c>
       <c r="K16" t="n">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="L16" t="n">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="M16" t="n">
-        <v>382</v>
+        <v>8359</v>
       </c>
       <c r="N16" t="n">
-        <v>2724</v>
+        <v>25210</v>
       </c>
       <c r="O16" t="n">
-        <v>11.02</v>
+        <v>12.33</v>
       </c>
       <c r="P16" t="n">
-        <v>13.67</v>
+        <v>9.27</v>
       </c>
       <c r="Q16" t="n">
-        <v>13.87</v>
+        <v>10.46</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Pidilite Industries Ltd</t>
+          <t>Infosys Ltd</t>
         </is>
       </c>
       <c r="S16" t="n">
-        <v>29.7</v>
+        <v>40</v>
       </c>
       <c r="T16" t="n">
-        <v>162274.18</v>
+        <v>1112279.92</v>
       </c>
       <c r="U16" t="n">
-        <v>36.12</v>
+        <v>35.99</v>
       </c>
       <c r="V16" t="n">
-        <v>12.3</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="W16" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1704,75 +1703,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>19.82</v>
+        <v>5.56</v>
       </c>
       <c r="D17" t="n">
-        <v>26.84</v>
+        <v>9.74</v>
       </c>
       <c r="E17" t="n">
-        <v>15.09</v>
+        <v>23.53</v>
       </c>
       <c r="F17" t="n">
-        <v>0.05</v>
+        <v>0.72</v>
       </c>
       <c r="G17" t="n">
-        <v>58.33</v>
+        <v>10.28</v>
       </c>
       <c r="H17" t="n">
-        <v>0.57</v>
+        <v>1.61</v>
       </c>
       <c r="I17" t="n">
-        <v>12898</v>
+        <v>102563</v>
       </c>
       <c r="J17" t="n">
-        <v>763</v>
+        <v>31464</v>
       </c>
       <c r="K17" t="n">
+        <v>30</v>
+      </c>
+      <c r="L17" t="n">
         <v>40</v>
       </c>
-      <c r="L17" t="n">
-        <v>34</v>
-      </c>
       <c r="M17" t="n">
-        <v>3274</v>
+        <v>132628</v>
       </c>
       <c r="N17" t="n">
-        <v>12135</v>
+        <v>71099</v>
       </c>
       <c r="O17" t="n">
-        <v>13.39</v>
+        <v>20.27</v>
       </c>
       <c r="P17" t="n">
-        <v>10.19</v>
+        <v>-15.86</v>
       </c>
       <c r="Q17" t="n">
-        <v>10.42</v>
+        <v>-14.54</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Sun Pharmaceuticals Industries Ltd</t>
+          <t xml:space="preserve">Indian Oil Corporation
+</t>
         </is>
       </c>
       <c r="S17" t="n">
-        <v>17.3</v>
+        <v>21.31</v>
       </c>
       <c r="T17" t="n">
-        <v>1339586.09</v>
+        <v>1418164.33</v>
       </c>
       <c r="U17" t="n">
-        <v>37.9</v>
+        <v>28.61</v>
       </c>
       <c r="V17" t="n">
-        <v>6.71</v>
+        <v>4.24</v>
       </c>
       <c r="W17" t="n">
-        <v>3.88</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1781,75 +1781,75 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>19.14</v>
+        <v>26.02</v>
       </c>
       <c r="D18" t="n">
-        <v>26.69</v>
+        <v>34.33</v>
       </c>
       <c r="E18" t="n">
-        <v>50.94</v>
+        <v>34.4</v>
       </c>
       <c r="F18" t="n">
-        <v>0.09</v>
+        <v>0.02</v>
       </c>
       <c r="G18" t="n">
-        <v>87.09999999999999</v>
+        <v>82.73999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>1.66</v>
+        <v>0.7</v>
       </c>
       <c r="I18" t="n">
-        <v>50429</v>
+        <v>1097</v>
       </c>
       <c r="J18" t="n">
-        <v>6091</v>
+        <v>215</v>
       </c>
       <c r="K18" t="n">
-        <v>127</v>
+        <v>14</v>
       </c>
       <c r="L18" t="n">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="M18" t="n">
-        <v>8021</v>
+        <v>60</v>
       </c>
       <c r="N18" t="n">
-        <v>44338</v>
+        <v>882</v>
       </c>
       <c r="O18" t="n">
-        <v>12.25</v>
+        <v>54.74</v>
       </c>
       <c r="P18" t="n">
-        <v>10.96</v>
+        <v>59.16</v>
       </c>
       <c r="Q18" t="n">
-        <v>11.64</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services Ltd</t>
+          <t>Indian Railway Catering &amp; Tourism Corporation Ltd</t>
         </is>
       </c>
       <c r="S18" t="n">
-        <v>64.3</v>
+        <v>53.8</v>
       </c>
       <c r="T18" t="n">
-        <v>461188.15</v>
+        <v>1258520.29</v>
       </c>
       <c r="U18" t="n">
-        <v>78.69</v>
+        <v>60.44</v>
       </c>
       <c r="V18" t="n">
-        <v>6.08</v>
+        <v>5.74</v>
       </c>
       <c r="W18" t="n">
-        <v>1.62</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1858,141 +1858,750 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>15.44</v>
+        <v>29.28</v>
       </c>
       <c r="D19" t="n">
-        <v>31.39</v>
+        <v>37.02</v>
       </c>
       <c r="E19" t="n">
-        <v>24.15</v>
+        <v>27.85</v>
       </c>
       <c r="F19" t="n">
-        <v>0.59</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>9.93</v>
+        <v>362.96</v>
       </c>
       <c r="H19" t="n">
-        <v>0.74</v>
+        <v>0.77</v>
       </c>
       <c r="I19" t="n">
-        <v>3426</v>
+        <v>18742</v>
       </c>
       <c r="J19" t="n">
-        <v>160</v>
+        <v>1563</v>
       </c>
       <c r="K19" t="n">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="L19" t="n">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="M19" t="n">
-        <v>4022</v>
+        <v>303</v>
       </c>
       <c r="N19" t="n">
-        <v>3266</v>
+        <v>17179</v>
       </c>
       <c r="O19" t="n">
-        <v>11.08</v>
+        <v>11.13</v>
       </c>
       <c r="P19" t="n">
-        <v>12.88</v>
+        <v>11.69</v>
       </c>
       <c r="Q19" t="n">
-        <v>12.77</v>
+        <v>9.82</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Torrent Pharmaceuticals Ltd</t>
+          <t xml:space="preserve">ITC Ltd
+</t>
         </is>
       </c>
       <c r="S19" t="n">
-        <v>23.2</v>
+        <v>34.76</v>
       </c>
       <c r="T19" t="n">
-        <v>1870170.39</v>
+        <v>332245.58</v>
       </c>
       <c r="U19" t="n">
-        <v>46.4</v>
+        <v>47.85</v>
       </c>
       <c r="V19" t="n">
-        <v>6.43</v>
+        <v>3.24</v>
       </c>
       <c r="W19" t="n">
-        <v>1.22</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="D20" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="E20" t="n">
+        <v>77.67</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="H20" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="I20" t="n">
+        <v>20445</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2179</v>
+      </c>
+      <c r="K20" t="n">
+        <v>95</v>
+      </c>
+      <c r="L20" t="n">
+        <v>36</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2071</v>
+      </c>
+      <c r="N20" t="n">
+        <v>18266</v>
+      </c>
+      <c r="O20" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="P20" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Larsen &amp; Toubro Ltd</t>
+        </is>
+      </c>
+      <c r="S20" t="n">
+        <v>17.18</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1124597.5</v>
+      </c>
+      <c r="U20" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="V20" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>LTIM</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>12.91</v>
+      </c>
+      <c r="D21" t="n">
+        <v>17.98</v>
+      </c>
+      <c r="E21" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>31.93</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="I21" t="n">
+        <v>9588</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3918</v>
+      </c>
+      <c r="K21" t="n">
+        <v>155</v>
+      </c>
+      <c r="L21" t="n">
+        <v>42</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2071</v>
+      </c>
+      <c r="N21" t="n">
+        <v>5670</v>
+      </c>
+      <c r="O21" t="n">
+        <v>31.62</v>
+      </c>
+      <c r="P21" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>LTIMindtree Ltd</t>
+        </is>
+      </c>
+      <c r="S21" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1347046.9</v>
+      </c>
+      <c r="U21" t="n">
+        <v>64.52</v>
+      </c>
+      <c r="V21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="W21" t="n">
+        <v>4.43</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="D22" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="E22" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>117.91</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="I22" t="n">
+        <v>28666</v>
+      </c>
+      <c r="J22" t="n">
+        <v>11865</v>
+      </c>
+      <c r="K22" t="n">
+        <v>429</v>
+      </c>
+      <c r="L22" t="n">
+        <v>29</v>
+      </c>
+      <c r="M22" t="n">
+        <v>119</v>
+      </c>
+      <c r="N22" t="n">
+        <v>16801</v>
+      </c>
+      <c r="O22" t="n">
+        <v>19.85</v>
+      </c>
+      <c r="P22" t="n">
+        <v>33.69</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>32.43</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Maruti Suzuki India Ltd</t>
+        </is>
+      </c>
+      <c r="S22" t="n">
+        <v>23.67</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1503863.63</v>
+      </c>
+      <c r="U22" t="n">
+        <v>20.78</v>
+      </c>
+      <c r="V22" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="D23" t="n">
+        <v>17.39</v>
+      </c>
+      <c r="E23" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G23" t="n">
+        <v>11.36</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="I23" t="n">
+        <v>156466</v>
+      </c>
+      <c r="J23" t="n">
+        <v>57203</v>
+      </c>
+      <c r="K23" t="n">
+        <v>39</v>
+      </c>
+      <c r="L23" t="n">
+        <v>31</v>
+      </c>
+      <c r="M23" t="n">
+        <v>153181</v>
+      </c>
+      <c r="N23" t="n">
+        <v>99263</v>
+      </c>
+      <c r="O23" t="n">
+        <v>21.34</v>
+      </c>
+      <c r="P23" t="n">
+        <v>18.64</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>26.22</v>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Oil &amp; Natural Gas Corpn Ltd</t>
+        </is>
+      </c>
+      <c r="S23" t="n">
+        <v>19.71</v>
+      </c>
+      <c r="T23" t="n">
+        <v>390111.05</v>
+      </c>
+      <c r="U23" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="V23" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>14.11</v>
+      </c>
+      <c r="D24" t="n">
+        <v>21.87</v>
+      </c>
+      <c r="E24" t="n">
+        <v>20.78</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G24" t="n">
+        <v>54.33</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="I24" t="n">
+        <v>4493</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1769</v>
+      </c>
+      <c r="K24" t="n">
+        <v>34</v>
+      </c>
+      <c r="L24" t="n">
+        <v>47</v>
+      </c>
+      <c r="M24" t="n">
+        <v>382</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2724</v>
+      </c>
+      <c r="O24" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="P24" t="n">
+        <v>15.05</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>14.64</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Pidilite Industries Ltd</t>
+        </is>
+      </c>
+      <c r="S24" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="T24" t="n">
+        <v>162274.18</v>
+      </c>
+      <c r="U24" t="n">
+        <v>36.12</v>
+      </c>
+      <c r="V24" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SIEMENS</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Sep 2024</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="D25" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="E25" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G25" t="n">
+        <v>67.15000000000001</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2172</v>
+      </c>
+      <c r="J25" t="n">
+        <v>502</v>
+      </c>
+      <c r="K25" t="n">
+        <v>76</v>
+      </c>
+      <c r="L25" t="n">
+        <v>16</v>
+      </c>
+      <c r="M25" t="n">
+        <v>279</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1670</v>
+      </c>
+      <c r="O25" t="n">
+        <v>22.28</v>
+      </c>
+      <c r="P25" t="n">
+        <v>37.11</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>36.33</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Siemens Ltd</t>
+        </is>
+      </c>
+      <c r="S25" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="D26" t="n">
+        <v>26.84</v>
+      </c>
+      <c r="E26" t="n">
+        <v>15.09</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G26" t="n">
+        <v>58.33</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="I26" t="n">
+        <v>12898</v>
+      </c>
+      <c r="J26" t="n">
+        <v>763</v>
+      </c>
+      <c r="K26" t="n">
+        <v>40</v>
+      </c>
+      <c r="L26" t="n">
+        <v>34</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3274</v>
+      </c>
+      <c r="N26" t="n">
+        <v>12135</v>
+      </c>
+      <c r="O26" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="P26" t="n">
+        <v>48.73</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>39.92</v>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Sun Pharmaceuticals Industries Ltd</t>
+        </is>
+      </c>
+      <c r="S26" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1339586.09</v>
+      </c>
+      <c r="U26" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="V26" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="W26" t="n">
+        <v>3.88</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>19.14</v>
+      </c>
+      <c r="D27" t="n">
+        <v>26.69</v>
+      </c>
+      <c r="E27" t="n">
+        <v>50.94</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="G27" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="I27" t="n">
+        <v>50429</v>
+      </c>
+      <c r="J27" t="n">
+        <v>6091</v>
+      </c>
+      <c r="K27" t="n">
+        <v>127</v>
+      </c>
+      <c r="L27" t="n">
+        <v>58</v>
+      </c>
+      <c r="M27" t="n">
+        <v>8021</v>
+      </c>
+      <c r="N27" t="n">
+        <v>44338</v>
+      </c>
+      <c r="O27" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="P27" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services Ltd</t>
+        </is>
+      </c>
+      <c r="S27" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="T27" t="n">
+        <v>461188.15</v>
+      </c>
+      <c r="U27" t="n">
+        <v>78.69</v>
+      </c>
+      <c r="V27" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>TRENT</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2024-03</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
         <v>11.94</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D28" t="n">
         <v>15.93</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E28" t="n">
         <v>36.31</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F28" t="n">
         <v>0.43</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G28" t="n">
         <v>8.039999999999999</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H28" t="n">
         <v>1.73</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I28" t="n">
         <v>1857</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J28" t="n">
         <v>508</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K28" t="n">
         <v>42</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L28" t="n">
         <v>8</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M28" t="n">
         <v>1753</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N28" t="n">
         <v>1349</v>
       </c>
-      <c r="O20" t="n">
-        <v>17.67</v>
-      </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr">
+      <c r="O28" t="n">
+        <v>55.15</v>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
         <is>
           <t>Trent Ltd</t>
         </is>
       </c>
-      <c r="S20" t="n">
+      <c r="S28" t="n">
         <v>23.8</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T28" t="n">
         <v>571322.04</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U28" t="n">
         <v>8.65</v>
       </c>
-      <c r="V20" t="n">
+      <c r="V28" t="n">
         <v>11.82</v>
       </c>
-      <c r="W20" t="n">
+      <c r="W28" t="n">
         <v>3.46</v>
       </c>
     </row>
@@ -2007,7 +2616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W6"/>
+  <dimension ref="A1:W17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2130,7 +2739,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ATGL</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2139,69 +2748,75 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>14.93</v>
+        <v>3.46</v>
       </c>
       <c r="D2" t="n">
-        <v>24.67</v>
+        <v>11.8</v>
       </c>
       <c r="E2" t="n">
-        <v>18.66</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>0.43</v>
+        <v>1.67</v>
       </c>
       <c r="G2" t="n">
-        <v>10.5</v>
+        <v>2.75</v>
       </c>
       <c r="H2" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+        <v>0.6</v>
+      </c>
+      <c r="I2" t="n">
+        <v>29079</v>
+      </c>
+      <c r="J2" t="n">
+        <v>18767</v>
+      </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="L2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>1557</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
+        <v>65310</v>
+      </c>
+      <c r="N2" t="n">
+        <v>10312</v>
+      </c>
       <c r="O2" t="n">
-        <v>19.66</v>
+        <v>26.83</v>
       </c>
       <c r="P2" t="n">
-        <v>22.43</v>
+        <v>55.31</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>57.32</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Adani Total Gas Ltd</t>
+          <t>Adani Enterprises Ltd</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>21.2</v>
+        <v>11.6</v>
       </c>
       <c r="T2" t="n">
-        <v>1535602.41</v>
+        <v>187927.97</v>
       </c>
       <c r="U2" t="n">
-        <v>56.96</v>
+        <v>58.87</v>
       </c>
       <c r="V2" t="n">
-        <v>5.76</v>
+        <v>10.41</v>
       </c>
       <c r="W2" t="n">
-        <v>0.51</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2210,75 +2825,75 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4.99</v>
+        <v>41.37</v>
       </c>
       <c r="D3" t="n">
-        <v>8.08</v>
+        <v>36.2</v>
       </c>
       <c r="E3" t="n">
-        <v>13.56</v>
+        <v>48.28</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03</v>
+        <v>0.8</v>
       </c>
       <c r="G3" t="n">
-        <v>73.29000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>2.4</v>
+        <v>0.55</v>
       </c>
       <c r="I3" t="n">
-        <v>5214</v>
+        <v>17651</v>
       </c>
       <c r="J3" t="n">
-        <v>2468</v>
+        <v>3481</v>
       </c>
       <c r="K3" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>592</v>
+        <v>34616</v>
       </c>
       <c r="N3" t="n">
-        <v>2746</v>
+        <v>14170</v>
       </c>
       <c r="O3" t="n">
-        <v>26.71</v>
+        <v>20.15</v>
       </c>
       <c r="P3" t="n">
-        <v>32.37</v>
+        <v>77.78</v>
       </c>
       <c r="Q3" t="n">
-        <v>28.88</v>
+        <v>82.12</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Avenue Supermarts Ltd</t>
+          <t>Adani Power Ltd</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>19.4</v>
+        <v>32.2</v>
       </c>
       <c r="T3" t="n">
-        <v>3053088.97</v>
+        <v>1372183.55</v>
       </c>
       <c r="U3" t="n">
-        <v>72.53</v>
+        <v>44.57</v>
       </c>
       <c r="V3" t="n">
-        <v>11.71</v>
+        <v>9.91</v>
       </c>
       <c r="W3" t="n">
-        <v>1.94</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2287,75 +2902,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26.02</v>
+        <v>4.91</v>
       </c>
       <c r="D4" t="n">
-        <v>34.33</v>
+        <v>12.56</v>
       </c>
       <c r="E4" t="n">
-        <v>34.4</v>
+        <v>13.48</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02</v>
+        <v>0.77</v>
       </c>
       <c r="G4" t="n">
-        <v>82.73999999999999</v>
+        <v>5.57</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7</v>
+        <v>1.14</v>
       </c>
       <c r="I4" t="n">
-        <v>1097</v>
+        <v>3457</v>
       </c>
       <c r="J4" t="n">
-        <v>215</v>
+        <v>1537</v>
       </c>
       <c r="K4" t="n">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="L4" t="n">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="M4" t="n">
-        <v>60</v>
+        <v>5333</v>
       </c>
       <c r="N4" t="n">
-        <v>882</v>
+        <v>1920</v>
       </c>
       <c r="O4" t="n">
-        <v>15.45</v>
+        <v>17.99</v>
       </c>
       <c r="P4" t="n">
-        <v>24.79</v>
+        <v>72.89</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.44</v>
+        <v>69.22</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Indian Railway Catering &amp; Tourism Corporation Ltd</t>
+          <t>Apollo Hospitals
+Chain of Indian private hospitals</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>53.8</v>
+        <v>17.2</v>
       </c>
       <c r="T4" t="n">
-        <v>1258520.29</v>
+        <v>1905622.43</v>
       </c>
       <c r="U4" t="n">
-        <v>60.44</v>
+        <v>47.72</v>
       </c>
       <c r="V4" t="n">
-        <v>5.74</v>
+        <v>7.68</v>
       </c>
       <c r="W4" t="n">
-        <v>1.08</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>BOSCHLTD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2364,144 +2980,988 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>86.52</v>
+        <v>14.89</v>
       </c>
       <c r="D5" t="n">
-        <v>84.04000000000001</v>
+        <v>12.52</v>
       </c>
       <c r="E5" t="n">
-        <v>1.15</v>
+        <v>20.64</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>198.8</v>
+        <v>71.78</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01</v>
+        <v>0.96</v>
       </c>
       <c r="I5" t="n">
-        <v>763</v>
+        <v>1536</v>
       </c>
       <c r="J5" t="n">
-        <v>1441</v>
+        <v>283</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>844</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="N5" t="n">
-        <v>-678</v>
+        <v>1253</v>
       </c>
       <c r="O5" t="n">
-        <v>561.3099999999999</v>
+        <v>15.26</v>
       </c>
       <c r="P5" t="n">
-        <v>619.99</v>
-      </c>
-      <c r="Q5" t="inlineStr"/>
+        <v>44.2</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>44.09</v>
+      </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Jio Financial Services Ltd</t>
+          <t>Bosch Ltd</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>2.16</v>
+        <v>20.6</v>
       </c>
       <c r="T5" t="n">
-        <v>1401774.99</v>
+        <v>2599556.05</v>
       </c>
       <c r="U5" t="n">
-        <v>34.24</v>
+        <v>58.43</v>
       </c>
       <c r="V5" t="n">
-        <v>9.91</v>
+        <v>6.47</v>
       </c>
       <c r="W5" t="n">
-        <v>3.09</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>DMART</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="D6" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="E6" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G6" t="n">
+        <v>73.29000000000001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5214</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2468</v>
+      </c>
+      <c r="K6" t="n">
+        <v>39</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>592</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2746</v>
+      </c>
+      <c r="O6" t="n">
+        <v>24.07</v>
+      </c>
+      <c r="P6" t="n">
+        <v>25.43</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>25.37</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Avenue Supermarts Ltd</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3053088.97</v>
+      </c>
+      <c r="U6" t="n">
+        <v>72.53</v>
+      </c>
+      <c r="V6" t="n">
+        <v>11.71</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.94</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>26.18</v>
+      </c>
+      <c r="E7" t="n">
+        <v>22.17</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G7" t="n">
+        <v>114.71</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="I7" t="n">
+        <v>6558</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2834</v>
+      </c>
+      <c r="K7" t="n">
+        <v>146</v>
+      </c>
+      <c r="L7" t="n">
+        <v>35</v>
+      </c>
+      <c r="M7" t="n">
+        <v>419</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3724</v>
+      </c>
+      <c r="O7" t="n">
+        <v>18.32</v>
+      </c>
+      <c r="P7" t="n">
+        <v>33.42</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>33.58</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Eicher Motors Ltd</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>222391.83</v>
+      </c>
+      <c r="U7" t="n">
+        <v>15.62</v>
+      </c>
+      <c r="V7" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="W7" t="n">
+        <v>4.41</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Jun 2015</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>20</v>
+      </c>
+      <c r="D8" t="n">
+        <v>23.12</v>
+      </c>
+      <c r="E8" t="n">
+        <v>30.31</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G8" t="n">
+        <v>105.63</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I8" t="n">
+        <v>7627</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2088</v>
+      </c>
+      <c r="K8" t="n">
+        <v>26</v>
+      </c>
+      <c r="L8" t="n">
+        <v>58</v>
+      </c>
+      <c r="M8" t="n">
+        <v>648</v>
+      </c>
+      <c r="N8" t="n">
+        <v>5539</v>
+      </c>
+      <c r="O8" t="n">
+        <v>38.72</v>
+      </c>
+      <c r="P8" t="n">
+        <v>32.15</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>33.22</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>HCL Technologies Ltd</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="T8" t="n">
+        <v>412593.29</v>
+      </c>
+      <c r="U8" t="n">
+        <v>63.63</v>
+      </c>
+      <c r="V8" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>26.02</v>
+      </c>
+      <c r="D9" t="n">
+        <v>34.33</v>
+      </c>
+      <c r="E9" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G9" t="n">
+        <v>82.73999999999999</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1097</v>
+      </c>
+      <c r="J9" t="n">
+        <v>215</v>
+      </c>
+      <c r="K9" t="n">
+        <v>14</v>
+      </c>
+      <c r="L9" t="n">
+        <v>47</v>
+      </c>
+      <c r="M9" t="n">
+        <v>60</v>
+      </c>
+      <c r="N9" t="n">
+        <v>882</v>
+      </c>
+      <c r="O9" t="n">
+        <v>54.74</v>
+      </c>
+      <c r="P9" t="n">
+        <v>59.16</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>65.48999999999999</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Indian Railway Catering &amp; Tourism Corporation Ltd</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1258520.29</v>
+      </c>
+      <c r="U9" t="n">
+        <v>60.44</v>
+      </c>
+      <c r="V9" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>LODHA</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2024-03</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
         <v>15.06</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D10" t="n">
         <v>25.83</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E10" t="n">
         <v>8.9</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F10" t="n">
         <v>0.44</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G10" t="n">
         <v>5.63</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H10" t="n">
         <v>0.22</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I10" t="n">
         <v>5459</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J10" t="n">
         <v>2947</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K10" t="n">
         <v>16</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L10" t="n">
         <v>14</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M10" t="n">
         <v>7698</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N10" t="n">
         <v>2512</v>
       </c>
-      <c r="O6" t="n">
-        <v>16.49</v>
-      </c>
-      <c r="P6" t="n">
-        <v>20.65</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>12.63</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="O10" t="n">
+        <v>25.63</v>
+      </c>
+      <c r="P10" t="n">
+        <v>168.94</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>123.61</v>
+      </c>
+      <c r="R10" t="inlineStr">
         <is>
           <t>Macrotech Developers Ltd</t>
         </is>
       </c>
-      <c r="S6" t="n">
+      <c r="S10" t="n">
         <v>11.1</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T10" t="n">
         <v>1209919.99</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U10" t="n">
         <v>51.95</v>
       </c>
-      <c r="V6" t="n">
+      <c r="V10" t="n">
         <v>7.65</v>
       </c>
-      <c r="W6" t="n">
+      <c r="W10" t="n">
         <v>4.05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>LTIM</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>12.91</v>
+      </c>
+      <c r="D11" t="n">
+        <v>17.98</v>
+      </c>
+      <c r="E11" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>31.93</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="I11" t="n">
+        <v>9588</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3918</v>
+      </c>
+      <c r="K11" t="n">
+        <v>155</v>
+      </c>
+      <c r="L11" t="n">
+        <v>42</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2071</v>
+      </c>
+      <c r="N11" t="n">
+        <v>5670</v>
+      </c>
+      <c r="O11" t="n">
+        <v>31.62</v>
+      </c>
+      <c r="P11" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>LTIMindtree Ltd</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1347046.9</v>
+      </c>
+      <c r="U11" t="n">
+        <v>64.52</v>
+      </c>
+      <c r="V11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="W11" t="n">
+        <v>4.43</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="D12" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="E12" t="n">
+        <v>18.54</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-15</v>
+      </c>
+      <c r="J12" t="n">
+        <v>5615</v>
+      </c>
+      <c r="K12" t="n">
+        <v>91</v>
+      </c>
+      <c r="L12" t="n">
+        <v>21</v>
+      </c>
+      <c r="M12" t="n">
+        <v>108647</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-5630</v>
+      </c>
+      <c r="O12" t="n">
+        <v>18.38</v>
+      </c>
+      <c r="P12" t="n">
+        <v>71.27</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>58.64</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mahindra &amp; Mahindra Ltd
+</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>26.98</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4173085.48</v>
+      </c>
+      <c r="U12" t="n">
+        <v>14.22</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.37</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="D13" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="E13" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>117.91</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="I13" t="n">
+        <v>28666</v>
+      </c>
+      <c r="J13" t="n">
+        <v>11865</v>
+      </c>
+      <c r="K13" t="n">
+        <v>429</v>
+      </c>
+      <c r="L13" t="n">
+        <v>29</v>
+      </c>
+      <c r="M13" t="n">
+        <v>119</v>
+      </c>
+      <c r="N13" t="n">
+        <v>16801</v>
+      </c>
+      <c r="O13" t="n">
+        <v>19.85</v>
+      </c>
+      <c r="P13" t="n">
+        <v>33.69</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>32.43</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Maruti Suzuki India Ltd</t>
+        </is>
+      </c>
+      <c r="S13" t="n">
+        <v>23.67</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1503863.63</v>
+      </c>
+      <c r="U13" t="n">
+        <v>20.78</v>
+      </c>
+      <c r="V13" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="D14" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="E14" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G14" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="I14" t="n">
+        <v>14213</v>
+      </c>
+      <c r="J14" t="n">
+        <v>6644</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4</v>
+      </c>
+      <c r="L14" t="n">
+        <v>20</v>
+      </c>
+      <c r="M14" t="n">
+        <v>19922</v>
+      </c>
+      <c r="N14" t="n">
+        <v>7569</v>
+      </c>
+      <c r="O14" t="n">
+        <v>17.51</v>
+      </c>
+      <c r="P14" t="n">
+        <v>27.32</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Samvardhana Motherson International Ltd</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="T14" t="n">
+        <v>146151.16</v>
+      </c>
+      <c r="U14" t="n">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="V14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.18</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SIEMENS</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sep 2024</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="D15" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="E15" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G15" t="n">
+        <v>67.15000000000001</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2172</v>
+      </c>
+      <c r="J15" t="n">
+        <v>502</v>
+      </c>
+      <c r="K15" t="n">
+        <v>76</v>
+      </c>
+      <c r="L15" t="n">
+        <v>16</v>
+      </c>
+      <c r="M15" t="n">
+        <v>279</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1670</v>
+      </c>
+      <c r="O15" t="n">
+        <v>22.28</v>
+      </c>
+      <c r="P15" t="n">
+        <v>37.11</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>36.33</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Siemens Ltd</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="D16" t="n">
+        <v>17.47</v>
+      </c>
+      <c r="E16" t="n">
+        <v>13.23</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I16" t="n">
+        <v>21623</v>
+      </c>
+      <c r="J16" t="n">
+        <v>9027</v>
+      </c>
+      <c r="K16" t="n">
+        <v>12</v>
+      </c>
+      <c r="L16" t="n">
+        <v>17</v>
+      </c>
+      <c r="M16" t="n">
+        <v>53689</v>
+      </c>
+      <c r="N16" t="n">
+        <v>12596</v>
+      </c>
+      <c r="O16" t="n">
+        <v>18.04</v>
+      </c>
+      <c r="P16" t="n">
+        <v>32.26</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tata Power Company Ltd
+</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1647269.48</v>
+      </c>
+      <c r="U16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="V16" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="D17" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="E17" t="n">
+        <v>37.22</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="G17" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1884</v>
+      </c>
+      <c r="J17" t="n">
+        <v>189</v>
+      </c>
+      <c r="K17" t="n">
+        <v>39</v>
+      </c>
+      <c r="L17" t="n">
+        <v>28</v>
+      </c>
+      <c r="M17" t="n">
+        <v>15528</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1695</v>
+      </c>
+      <c r="O17" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="P17" t="n">
+        <v>35.08</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>35.43</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Titan Company Ltd
+</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1793769.72</v>
+      </c>
+      <c r="U17" t="n">
+        <v>10.13</v>
+      </c>
+      <c r="V17" t="n">
+        <v>10.51</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.1</v>
       </c>
     </row>
   </sheetData>
@@ -2683,13 +4143,13 @@
         <v>1253</v>
       </c>
       <c r="O2" t="n">
-        <v>5.86</v>
+        <v>15.26</v>
       </c>
       <c r="P2" t="n">
-        <v>6.69</v>
+        <v>44.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.26</v>
+        <v>44.09</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -2760,13 +4220,13 @@
         <v>2407</v>
       </c>
       <c r="O3" t="n">
-        <v>15.79</v>
+        <v>17.65</v>
       </c>
       <c r="P3" t="n">
-        <v>17.79</v>
+        <v>14.34</v>
       </c>
       <c r="Q3" t="n">
-        <v>16.69</v>
+        <v>12.36</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -2837,13 +4297,13 @@
         <v>17179</v>
       </c>
       <c r="O4" t="n">
-        <v>7.48</v>
+        <v>11.13</v>
       </c>
       <c r="P4" t="n">
-        <v>8.640000000000001</v>
+        <v>11.69</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.52</v>
+        <v>9.82</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -2915,10 +4375,10 @@
         <v>26122</v>
       </c>
       <c r="O5" t="n">
-        <v>7.78</v>
+        <v>6.72</v>
       </c>
       <c r="P5" t="n">
-        <v>58.38</v>
+        <v>93.23999999999999</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -2990,13 +4450,13 @@
         <v>16801</v>
       </c>
       <c r="O6" t="n">
-        <v>10.4</v>
+        <v>19.85</v>
       </c>
       <c r="P6" t="n">
-        <v>15.57</v>
+        <v>33.69</v>
       </c>
       <c r="Q6" t="n">
-        <v>15.16</v>
+        <v>32.43</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -3198,13 +4658,13 @@
         <v>-5630</v>
       </c>
       <c r="O2" t="n">
-        <v>6.48</v>
+        <v>18.38</v>
       </c>
       <c r="P2" t="n">
-        <v>10.04</v>
+        <v>71.27</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.210000000000001</v>
+        <v>58.64</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -3276,13 +4736,13 @@
         <v>7569</v>
       </c>
       <c r="O3" t="n">
-        <v>12.98</v>
+        <v>17.51</v>
       </c>
       <c r="P3" t="n">
-        <v>20.23</v>
+        <v>27.32</v>
       </c>
       <c r="Q3" t="n">
-        <v>16.1</v>
+        <v>31.61</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -3484,13 +4944,13 @@
         <v>6104</v>
       </c>
       <c r="O2" t="n">
-        <v>10.51</v>
+        <v>12.54</v>
       </c>
       <c r="P2" t="n">
-        <v>12.23</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.25</v>
+        <v>9.82</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -3562,13 +5022,13 @@
         <v>-5555</v>
       </c>
       <c r="O3" t="n">
-        <v>13.22</v>
+        <v>17.48</v>
       </c>
       <c r="P3" t="n">
-        <v>14.53</v>
+        <v>41.47</v>
       </c>
       <c r="Q3" t="n">
-        <v>11.92</v>
+        <v>40.2</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -3639,13 +5099,13 @@
         <v>6558</v>
       </c>
       <c r="O4" t="n">
-        <v>7.72</v>
+        <v>15.22</v>
       </c>
       <c r="P4" t="n">
-        <v>7.39</v>
+        <v>10.99</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.7</v>
+        <v>11.86</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -3716,13 +5176,13 @@
         <v>1253</v>
       </c>
       <c r="O5" t="n">
-        <v>5.86</v>
+        <v>15.26</v>
       </c>
       <c r="P5" t="n">
-        <v>6.69</v>
+        <v>44.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.26</v>
+        <v>44.09</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -3793,13 +5253,13 @@
         <v>15046</v>
       </c>
       <c r="O6" t="n">
-        <v>11.02</v>
+        <v>14.18</v>
       </c>
       <c r="P6" t="n">
-        <v>15.32</v>
+        <v>53.86</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.44</v>
+        <v>45.65</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -3870,13 +5330,13 @@
         <v>18103</v>
       </c>
       <c r="O7" t="n">
-        <v>6.18</v>
+        <v>11.74</v>
       </c>
       <c r="P7" t="n">
-        <v>5.85</v>
+        <v>28.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.27</v>
+        <v>27.79</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -3947,13 +5407,13 @@
         <v>2013</v>
       </c>
       <c r="O8" t="n">
-        <v>6.07</v>
+        <v>6.81</v>
       </c>
       <c r="P8" t="n">
-        <v>7.18</v>
+        <v>0.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.93</v>
+        <v>0</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -4024,13 +5484,13 @@
         <v>3724</v>
       </c>
       <c r="O9" t="n">
-        <v>8.539999999999999</v>
+        <v>18.32</v>
       </c>
       <c r="P9" t="n">
-        <v>20.08</v>
+        <v>33.42</v>
       </c>
       <c r="Q9" t="n">
-        <v>23.83</v>
+        <v>33.58</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -4101,13 +5561,13 @@
         <v>8226</v>
       </c>
       <c r="O10" t="n">
-        <v>6.69</v>
+        <v>8.02</v>
       </c>
       <c r="P10" t="n">
-        <v>9.050000000000001</v>
+        <v>27.17</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2</v>
+        <v>27.54</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -4178,13 +5638,13 @@
         <v>1953</v>
       </c>
       <c r="O11" t="n">
-        <v>9.27</v>
+        <v>18.58</v>
       </c>
       <c r="P11" t="n">
-        <v>7.6</v>
+        <v>7.61</v>
       </c>
       <c r="Q11" t="n">
-        <v>7.73</v>
+        <v>6.66</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -4255,13 +5715,13 @@
         <v>15469</v>
       </c>
       <c r="O12" t="n">
-        <v>7.27</v>
+        <v>7.44</v>
       </c>
       <c r="P12" t="n">
-        <v>8.970000000000001</v>
+        <v>7.69</v>
       </c>
       <c r="Q12" t="n">
-        <v>8.130000000000001</v>
+        <v>7.85</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -4333,13 +5793,13 @@
         <v>157284</v>
       </c>
       <c r="O13" t="n">
-        <v>12.3</v>
+        <v>19.29</v>
       </c>
       <c r="P13" t="n">
-        <v>14.68</v>
+        <v>26.66</v>
       </c>
       <c r="Q13" t="n">
-        <v>13.7</v>
+        <v>26.89</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -4410,13 +5870,13 @@
         <v>2407</v>
       </c>
       <c r="O14" t="n">
-        <v>15.79</v>
+        <v>17.65</v>
       </c>
       <c r="P14" t="n">
-        <v>17.79</v>
+        <v>14.34</v>
       </c>
       <c r="Q14" t="n">
-        <v>16.69</v>
+        <v>12.36</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -4487,14 +5947,10 @@
         <v>21183</v>
       </c>
       <c r="O15" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="P15" t="n">
-        <v>18.57</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>-34.6</v>
-      </c>
+        <v>51.18</v>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
           <t>Interglobe Aviation Ltd</t>
@@ -4564,13 +6020,13 @@
         <v>25210</v>
       </c>
       <c r="O16" t="n">
-        <v>12.16</v>
+        <v>12.33</v>
       </c>
       <c r="P16" t="n">
-        <v>9.390000000000001</v>
+        <v>9.27</v>
       </c>
       <c r="Q16" t="n">
-        <v>10.15</v>
+        <v>10.46</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -4641,13 +6097,13 @@
         <v>17179</v>
       </c>
       <c r="O17" t="n">
-        <v>7.48</v>
+        <v>11.13</v>
       </c>
       <c r="P17" t="n">
-        <v>8.640000000000001</v>
+        <v>11.69</v>
       </c>
       <c r="Q17" t="n">
-        <v>8.52</v>
+        <v>9.82</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -4719,10 +6175,10 @@
         <v>26122</v>
       </c>
       <c r="O18" t="n">
-        <v>7.78</v>
+        <v>6.72</v>
       </c>
       <c r="P18" t="n">
-        <v>58.38</v>
+        <v>93.23999999999999</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -4794,13 +6250,13 @@
         <v>5670</v>
       </c>
       <c r="O19" t="n">
-        <v>20.78</v>
+        <v>31.62</v>
       </c>
       <c r="P19" t="n">
-        <v>19.09</v>
+        <v>23.95</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.01</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -4871,13 +6327,13 @@
         <v>4175</v>
       </c>
       <c r="O20" t="n">
-        <v>6.69</v>
+        <v>7.64</v>
       </c>
       <c r="P20" t="n">
-        <v>9.51</v>
+        <v>11.92</v>
       </c>
       <c r="Q20" t="n">
-        <v>9.07</v>
+        <v>11.5</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -4948,13 +6404,13 @@
         <v>37290</v>
       </c>
       <c r="O21" t="n">
-        <v>11.01</v>
+        <v>3.68</v>
       </c>
       <c r="P21" t="n">
-        <v>11.37</v>
+        <v>6.89</v>
       </c>
       <c r="Q21" t="n">
-        <v>10.74</v>
+        <v>6.94</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -5025,13 +6481,13 @@
         <v>12135</v>
       </c>
       <c r="O22" t="n">
-        <v>13.39</v>
+        <v>10.7</v>
       </c>
       <c r="P22" t="n">
-        <v>10.19</v>
+        <v>48.73</v>
       </c>
       <c r="Q22" t="n">
-        <v>10.42</v>
+        <v>39.92</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
@@ -5102,14 +6558,10 @@
         <v>67915</v>
       </c>
       <c r="O23" t="n">
-        <v>7.31</v>
-      </c>
-      <c r="P23" t="n">
-        <v>10.71</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>9.050000000000001</v>
-      </c>
+        <v>15.21</v>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
           <t>Tata Motors Ltd</t>
@@ -5179,13 +6631,13 @@
         <v>1695</v>
       </c>
       <c r="O24" t="n">
-        <v>15.05</v>
+        <v>25.95</v>
       </c>
       <c r="P24" t="n">
-        <v>13.3</v>
+        <v>35.08</v>
       </c>
       <c r="Q24" t="n">
-        <v>13.61</v>
+        <v>35.43</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
@@ -5257,7 +6709,7 @@
         <v>1349</v>
       </c>
       <c r="O25" t="n">
-        <v>17.67</v>
+        <v>55.15</v>
       </c>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
@@ -5293,7 +6745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W57"/>
+  <dimension ref="A1:W52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5461,13 +6913,13 @@
         <v>1213</v>
       </c>
       <c r="O2" t="n">
-        <v>11.44</v>
+        <v>8.92</v>
       </c>
       <c r="P2" t="n">
-        <v>19.94</v>
+        <v>16.78</v>
       </c>
       <c r="Q2" t="n">
-        <v>19.98</v>
+        <v>16.81</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -5538,13 +6990,13 @@
         <v>10312</v>
       </c>
       <c r="O3" t="n">
-        <v>6.82</v>
+        <v>26.83</v>
       </c>
       <c r="P3" t="n">
-        <v>14.35</v>
+        <v>55.31</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.37</v>
+        <v>57.32</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -5615,13 +7067,13 @@
         <v>15018</v>
       </c>
       <c r="O4" t="n">
-        <v>18.86</v>
+        <v>22.7</v>
       </c>
       <c r="P4" t="n">
-        <v>16.01</v>
+        <v>17.86</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.48</v>
+        <v>15.83</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -5648,317 +7100,317 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AMBUJACEM</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3 15-03</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7.77</v>
+        <v>41.37</v>
       </c>
       <c r="D5" t="n">
-        <v>13.15</v>
+        <v>36.2</v>
       </c>
       <c r="E5" t="n">
-        <v>11.43</v>
+        <v>48.28</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02</v>
+        <v>0.8</v>
       </c>
       <c r="G5" t="n">
-        <v>28.56</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>0.51</v>
+        <v>0.55</v>
       </c>
       <c r="I5" t="n">
-        <v>14587</v>
+        <v>17651</v>
       </c>
       <c r="J5" t="n">
-        <v>8941</v>
+        <v>3481</v>
       </c>
       <c r="K5" t="n">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="L5" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>699</v>
+        <v>34616</v>
       </c>
       <c r="N5" t="n">
-        <v>5646</v>
+        <v>14170</v>
       </c>
       <c r="O5" t="n">
-        <v>10.65</v>
+        <v>20.15</v>
       </c>
       <c r="P5" t="n">
-        <v>9.58</v>
+        <v>77.78</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.13</v>
+        <v>82.12</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Ambuja Cements Ltd</t>
+          <t>Adani Power Ltd</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>12.8</v>
+        <v>32.2</v>
       </c>
       <c r="T5" t="n">
-        <v>1281411.04</v>
+        <v>1372183.55</v>
       </c>
       <c r="U5" t="n">
-        <v>55.62</v>
+        <v>44.57</v>
       </c>
       <c r="V5" t="n">
-        <v>9.210000000000001</v>
+        <v>9.91</v>
       </c>
       <c r="W5" t="n">
-        <v>3.1</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>AMBUJACEM</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>3 15-03</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="D6" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="E6" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G6" t="n">
+        <v>28.56</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="I6" t="n">
+        <v>14587</v>
+      </c>
+      <c r="J6" t="n">
+        <v>8941</v>
+      </c>
+      <c r="K6" t="n">
+        <v>13</v>
+      </c>
+      <c r="L6" t="n">
+        <v>19</v>
+      </c>
+      <c r="M6" t="n">
+        <v>699</v>
+      </c>
+      <c r="N6" t="n">
+        <v>5646</v>
+      </c>
+      <c r="O6" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="P6" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Ambuja Cements Ltd</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1281411.04</v>
+      </c>
+      <c r="U6" t="n">
+        <v>55.62</v>
+      </c>
+      <c r="V6" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="W6" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>APOLLOHOSP</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2024-03</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
         <v>4.91</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D7" t="n">
         <v>12.56</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E7" t="n">
         <v>13.48</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F7" t="n">
         <v>0.77</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G7" t="n">
         <v>5.57</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H7" t="n">
         <v>1.14</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I7" t="n">
         <v>3457</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J7" t="n">
         <v>1537</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K7" t="n">
         <v>63</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L7" t="n">
         <v>26</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M7" t="n">
         <v>5333</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N7" t="n">
         <v>1920</v>
       </c>
-      <c r="O6" t="n">
-        <v>15.14</v>
-      </c>
-      <c r="P6" t="n">
-        <v>12.34</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>11.59</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="O7" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="P7" t="n">
+        <v>72.89</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>69.22</v>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>Apollo Hospitals
 Chain of Indian private hospitals</t>
         </is>
       </c>
-      <c r="S6" t="n">
+      <c r="S7" t="n">
         <v>17.2</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T7" t="n">
         <v>1905622.43</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>47.72</v>
       </c>
-      <c r="V6" t="n">
+      <c r="V7" t="n">
         <v>7.68</v>
       </c>
-      <c r="W6" t="n">
+      <c r="W7" t="n">
         <v>3.22</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>ASIANPAINT</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2024-03</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
         <v>15.66</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D8" t="n">
         <v>21.37</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E8" t="n">
         <v>29.68</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F8" t="n">
         <v>0.13</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G8" t="n">
         <v>41</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H8" t="n">
         <v>1.19</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I8" t="n">
         <v>8652</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J8" t="n">
         <v>2548</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K8" t="n">
         <v>57</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L8" t="n">
         <v>58</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M8" t="n">
         <v>2474</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N8" t="n">
         <v>6104</v>
       </c>
-      <c r="O7" t="n">
-        <v>10.51</v>
-      </c>
-      <c r="P7" t="n">
-        <v>12.23</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="O8" t="n">
+        <v>12.54</v>
+      </c>
+      <c r="P8" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>Asian Paints
 Indian Multi-National Paint and Coating Manufacturing Company</t>
         </is>
       </c>
-      <c r="S7" t="n">
+      <c r="S8" t="n">
         <v>41.75</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T8" t="n">
         <v>2126725.18</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>73.37</v>
       </c>
-      <c r="V7" t="n">
+      <c r="V8" t="n">
         <v>3.9</v>
       </c>
-      <c r="W7" t="n">
+      <c r="W8" t="n">
         <v>2.42</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>BAJAJ-AUTO</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2024-03</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>17.18</v>
-      </c>
-      <c r="D8" t="n">
-        <v>19.53</v>
-      </c>
-      <c r="E8" t="n">
-        <v>26.61</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G8" t="n">
-        <v>174.42</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="I8" t="n">
-        <v>6630</v>
-      </c>
-      <c r="J8" t="n">
-        <v>72</v>
-      </c>
-      <c r="K8" t="n">
-        <v>276</v>
-      </c>
-      <c r="L8" t="n">
-        <v>29</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1912</v>
-      </c>
-      <c r="N8" t="n">
-        <v>6558</v>
-      </c>
-      <c r="O8" t="n">
-        <v>7.72</v>
-      </c>
-      <c r="P8" t="n">
-        <v>7.39</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>Bajaj Auto Ltd</t>
-        </is>
-      </c>
-      <c r="S8" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>653817.3</v>
-      </c>
-      <c r="U8" t="n">
-        <v>29.91</v>
-      </c>
-      <c r="V8" t="n">
-        <v>9.83</v>
-      </c>
-      <c r="W8" t="n">
-        <v>3.59</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5967,75 +7419,75 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>432.73</v>
+        <v>17.18</v>
       </c>
       <c r="D9" t="n">
-        <v>91.77</v>
+        <v>19.53</v>
       </c>
       <c r="E9" t="n">
-        <v>13.58</v>
+        <v>26.61</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>3764.5</v>
+        <v>174.42</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03</v>
+        <v>1.14</v>
       </c>
       <c r="I9" t="n">
-        <v>2413</v>
+        <v>6630</v>
       </c>
       <c r="J9" t="n">
-        <v>472</v>
+        <v>72</v>
       </c>
       <c r="K9" t="n">
-        <v>653</v>
+        <v>276</v>
       </c>
       <c r="L9" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="M9" t="n">
-        <v>63</v>
+        <v>1912</v>
       </c>
       <c r="N9" t="n">
-        <v>1941</v>
+        <v>6558</v>
       </c>
       <c r="O9" t="n">
-        <v>14.62</v>
+        <v>15.22</v>
       </c>
       <c r="P9" t="n">
-        <v>12.32</v>
+        <v>10.99</v>
       </c>
       <c r="Q9" t="n">
-        <v>12.22</v>
+        <v>11.86</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Bajaj Holdings &amp; Investment Ltd</t>
+          <t>Bajaj Auto Ltd</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>13.1</v>
+        <v>33.5</v>
       </c>
       <c r="T9" t="n">
-        <v>2191568.13</v>
+        <v>653817.3</v>
       </c>
       <c r="U9" t="n">
-        <v>37.73</v>
+        <v>29.91</v>
       </c>
       <c r="V9" t="n">
-        <v>9.380000000000001</v>
+        <v>9.83</v>
       </c>
       <c r="W9" t="n">
-        <v>3.37</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -6044,75 +7496,75 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>19.66</v>
+        <v>432.73</v>
       </c>
       <c r="D10" t="n">
-        <v>24.92</v>
+        <v>91.77</v>
       </c>
       <c r="E10" t="n">
-        <v>4744.05</v>
+        <v>13.58</v>
       </c>
       <c r="F10" t="n">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>476.75</v>
+        <v>3764.5</v>
       </c>
       <c r="H10" t="n">
-        <v>125.89</v>
+        <v>0.03</v>
       </c>
       <c r="I10" t="n">
-        <v>10583</v>
+        <v>2413</v>
       </c>
       <c r="J10" t="n">
-        <v>5924</v>
+        <v>472</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>653</v>
       </c>
       <c r="L10" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="M10" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="N10" t="n">
-        <v>4659</v>
+        <v>1941</v>
       </c>
       <c r="O10" t="n">
-        <v>10.84</v>
+        <v>39.55</v>
       </c>
       <c r="P10" t="n">
-        <v>14.32</v>
+        <v>19.64</v>
       </c>
       <c r="Q10" t="n">
-        <v>16.1</v>
+        <v>19.37</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Bharat Electronics Ltd</t>
+          <t>Bajaj Holdings &amp; Investment Ltd</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>34.6</v>
+        <v>13.1</v>
       </c>
       <c r="T10" t="n">
-        <v>1354781.06</v>
+        <v>2191568.13</v>
       </c>
       <c r="U10" t="n">
-        <v>17.89</v>
+        <v>37.73</v>
       </c>
       <c r="V10" t="n">
-        <v>9.220000000000001</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>0.76</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -6121,69 +7573,69 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5.71</v>
+        <v>19.66</v>
       </c>
       <c r="D11" t="n">
-        <v>52.2</v>
+        <v>24.92</v>
       </c>
       <c r="E11" t="n">
-        <v>10.36</v>
+        <v>4744.05</v>
       </c>
       <c r="F11" t="n">
-        <v>2.61</v>
+        <v>0.51</v>
       </c>
       <c r="G11" t="n">
-        <v>3.31</v>
+        <v>476.75</v>
       </c>
       <c r="H11" t="n">
-        <v>0.34</v>
+        <v>125.89</v>
       </c>
       <c r="I11" t="n">
-        <v>129987</v>
+        <v>10583</v>
       </c>
       <c r="J11" t="n">
-        <v>51089</v>
+        <v>5924</v>
       </c>
       <c r="K11" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="L11" t="n">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="M11" t="n">
-        <v>215592</v>
+        <v>43</v>
       </c>
       <c r="N11" t="n">
-        <v>78898</v>
+        <v>4659</v>
       </c>
       <c r="O11" t="n">
-        <v>6.04</v>
+        <v>11.2</v>
       </c>
       <c r="P11" t="n">
-        <v>16.25</v>
+        <v>21.26</v>
       </c>
       <c r="Q11" t="n">
-        <v>15.26</v>
+        <v>18.92</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Bharti Airtel Ltd</t>
+          <t>Bharat Electronics Ltd</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>13.1</v>
+        <v>34.6</v>
       </c>
       <c r="T11" t="n">
-        <v>378605.83</v>
+        <v>1354781.06</v>
       </c>
       <c r="U11" t="n">
-        <v>63.78</v>
+        <v>17.89</v>
       </c>
       <c r="V11" t="n">
-        <v>6.28</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="12">
@@ -6234,13 +7686,13 @@
         <v>1253</v>
       </c>
       <c r="O12" t="n">
-        <v>5.86</v>
+        <v>15.26</v>
       </c>
       <c r="P12" t="n">
-        <v>6.69</v>
+        <v>44.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.26</v>
+        <v>44.09</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -6266,7 +7718,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6275,75 +7727,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5.99</v>
+        <v>16.12</v>
       </c>
       <c r="D13" t="n">
-        <v>9.84</v>
+        <v>75.59</v>
       </c>
       <c r="E13" t="n">
-        <v>35.51</v>
+        <v>15.55</v>
       </c>
       <c r="F13" t="n">
-        <v>0.72</v>
+        <v>0.02</v>
       </c>
       <c r="G13" t="n">
-        <v>11.36</v>
+        <v>35.34</v>
       </c>
       <c r="H13" t="n">
-        <v>2.21</v>
+        <v>0.79</v>
       </c>
       <c r="I13" t="n">
-        <v>46457</v>
+        <v>7116</v>
       </c>
       <c r="J13" t="n">
-        <v>10521</v>
+        <v>2982</v>
       </c>
       <c r="K13" t="n">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="L13" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="M13" t="n">
-        <v>54599</v>
+        <v>559</v>
       </c>
       <c r="N13" t="n">
-        <v>35936</v>
+        <v>4134</v>
       </c>
       <c r="O13" t="n">
-        <v>5.21</v>
+        <v>8.93</v>
       </c>
       <c r="P13" t="n">
-        <v>17.74</v>
+        <v>20.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>18.92</v>
+        <v>19.9</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Bharat Petroleum Corporation Ltd</t>
+          <t xml:space="preserve">Cipla Ltd
+</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>32.1</v>
+        <v>22.8</v>
       </c>
       <c r="T13" t="n">
-        <v>468662.13</v>
+        <v>439803.15</v>
       </c>
       <c r="U13" t="n">
-        <v>68.15000000000001</v>
+        <v>59.75</v>
       </c>
       <c r="V13" t="n">
-        <v>0.72</v>
+        <v>5.93</v>
       </c>
       <c r="W13" t="n">
-        <v>1.15</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6352,75 +7805,75 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>12.73</v>
+        <v>26.26</v>
       </c>
       <c r="D14" t="n">
-        <v>18.89</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>54.15</v>
+        <v>45.17</v>
       </c>
       <c r="F14" t="n">
-        <v>0.52</v>
+        <v>0.08</v>
       </c>
       <c r="G14" t="n">
-        <v>20.6</v>
+        <v>11.24</v>
       </c>
       <c r="H14" t="n">
-        <v>1.85</v>
+        <v>0.6</v>
       </c>
       <c r="I14" t="n">
-        <v>3050</v>
+        <v>22589</v>
       </c>
       <c r="J14" t="n">
-        <v>477</v>
+        <v>4486</v>
       </c>
       <c r="K14" t="n">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="L14" t="n">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="M14" t="n">
-        <v>2065</v>
+        <v>6523</v>
       </c>
       <c r="N14" t="n">
-        <v>2573</v>
+        <v>18103</v>
       </c>
       <c r="O14" t="n">
-        <v>8.92</v>
+        <v>11.74</v>
       </c>
       <c r="P14" t="n">
-        <v>19.15</v>
+        <v>28.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>19.03</v>
+        <v>27.79</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>Britannia Industries Ltd</t>
+          <t>Coal India Ltd</t>
         </is>
       </c>
       <c r="S14" t="n">
-        <v>48.9</v>
+        <v>63.6</v>
       </c>
       <c r="T14" t="n">
-        <v>324745.74</v>
+        <v>454024.84</v>
       </c>
       <c r="U14" t="n">
-        <v>63.91</v>
+        <v>34.27</v>
       </c>
       <c r="V14" t="n">
-        <v>4.26</v>
+        <v>14.75</v>
       </c>
       <c r="W14" t="n">
-        <v>1.88</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6429,76 +7882,75 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16.12</v>
+        <v>42.38</v>
       </c>
       <c r="D15" t="n">
-        <v>75.59</v>
+        <v>33.05</v>
       </c>
       <c r="E15" t="n">
-        <v>15.55</v>
+        <v>6.91</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02</v>
+        <v>0.12</v>
       </c>
       <c r="G15" t="n">
-        <v>35.34</v>
+        <v>7.46</v>
       </c>
       <c r="H15" t="n">
-        <v>0.79</v>
+        <v>0.11</v>
       </c>
       <c r="I15" t="n">
-        <v>7116</v>
+        <v>4068</v>
       </c>
       <c r="J15" t="n">
-        <v>2982</v>
+        <v>1529</v>
       </c>
       <c r="K15" t="n">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="L15" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="M15" t="n">
-        <v>559</v>
+        <v>4834</v>
       </c>
       <c r="N15" t="n">
-        <v>4134</v>
+        <v>2539</v>
       </c>
       <c r="O15" t="n">
-        <v>10.35</v>
+        <v>6.64</v>
       </c>
       <c r="P15" t="n">
-        <v>10.26</v>
+        <v>38.66</v>
       </c>
       <c r="Q15" t="n">
-        <v>10.36</v>
+        <v>41.42</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cipla Ltd
-</t>
+          <t>DLF Ltd</t>
         </is>
       </c>
       <c r="S15" t="n">
-        <v>22.8</v>
+        <v>5.74</v>
       </c>
       <c r="T15" t="n">
-        <v>439803.15</v>
+        <v>1381712.03</v>
       </c>
       <c r="U15" t="n">
-        <v>59.75</v>
+        <v>46.26</v>
       </c>
       <c r="V15" t="n">
-        <v>5.93</v>
+        <v>14.32</v>
       </c>
       <c r="W15" t="n">
-        <v>0.12</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>DMART</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6507,75 +7959,75 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>26.26</v>
+        <v>4.99</v>
       </c>
       <c r="D16" t="n">
-        <v>66.29000000000001</v>
+        <v>8.08</v>
       </c>
       <c r="E16" t="n">
-        <v>45.17</v>
+        <v>13.56</v>
       </c>
       <c r="F16" t="n">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="G16" t="n">
-        <v>11.24</v>
+        <v>73.29000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="I16" t="n">
-        <v>22589</v>
+        <v>5214</v>
       </c>
       <c r="J16" t="n">
-        <v>4486</v>
+        <v>2468</v>
       </c>
       <c r="K16" t="n">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="L16" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>6523</v>
+        <v>592</v>
       </c>
       <c r="N16" t="n">
-        <v>18103</v>
+        <v>2746</v>
       </c>
       <c r="O16" t="n">
-        <v>6.18</v>
+        <v>24.07</v>
       </c>
       <c r="P16" t="n">
-        <v>5.85</v>
+        <v>25.43</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.27</v>
+        <v>25.37</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Coal India Ltd</t>
+          <t>Avenue Supermarts Ltd</t>
         </is>
       </c>
       <c r="S16" t="n">
-        <v>63.6</v>
+        <v>19.4</v>
       </c>
       <c r="T16" t="n">
-        <v>454024.84</v>
+        <v>3053088.97</v>
       </c>
       <c r="U16" t="n">
-        <v>34.27</v>
+        <v>72.53</v>
       </c>
       <c r="V16" t="n">
-        <v>14.75</v>
+        <v>11.71</v>
       </c>
       <c r="W16" t="n">
-        <v>4.38</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -6584,75 +8036,75 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>14.6</v>
+        <v>19.91</v>
       </c>
       <c r="D17" t="n">
-        <v>19.35</v>
+        <v>28.32</v>
       </c>
       <c r="E17" t="n">
-        <v>18.36</v>
+        <v>19.74</v>
       </c>
       <c r="F17" t="n">
-        <v>0.14</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>23.24</v>
+        <v>51.71</v>
       </c>
       <c r="H17" t="n">
-        <v>0.82</v>
+        <v>0.72</v>
       </c>
       <c r="I17" t="n">
-        <v>2984</v>
+        <v>8577</v>
       </c>
       <c r="J17" t="n">
-        <v>971</v>
+        <v>4034</v>
       </c>
       <c r="K17" t="n">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="L17" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="M17" t="n">
-        <v>1365</v>
+        <v>2002</v>
       </c>
       <c r="N17" t="n">
-        <v>2013</v>
+        <v>4543</v>
       </c>
       <c r="O17" t="n">
-        <v>6.07</v>
+        <v>13.16</v>
       </c>
       <c r="P17" t="n">
-        <v>7.18</v>
+        <v>29.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>7.93</v>
+        <v>29.16</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Dabur India Ltd</t>
+          <t>Dr Reddys Laboratories Ltd</t>
         </is>
       </c>
       <c r="S17" t="n">
-        <v>22.3</v>
+        <v>26.5</v>
       </c>
       <c r="T17" t="n">
-        <v>56521.84</v>
+        <v>2441803.28</v>
       </c>
       <c r="U17" t="n">
-        <v>50.95</v>
+        <v>11.73</v>
       </c>
       <c r="V17" t="n">
-        <v>13.59</v>
+        <v>10.19</v>
       </c>
       <c r="W17" t="n">
-        <v>3.42</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -6661,75 +8113,75 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>20.4</v>
+        <v>24.2</v>
       </c>
       <c r="D18" t="n">
-        <v>28.17</v>
+        <v>26.18</v>
       </c>
       <c r="E18" t="n">
-        <v>11.79</v>
+        <v>22.17</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="G18" t="n">
-        <v>636.25</v>
+        <v>114.71</v>
       </c>
       <c r="H18" t="n">
-        <v>0.51</v>
+        <v>0.72</v>
       </c>
       <c r="I18" t="n">
-        <v>1530</v>
+        <v>6558</v>
       </c>
       <c r="J18" t="n">
-        <v>269</v>
+        <v>2834</v>
       </c>
       <c r="K18" t="n">
-        <v>60</v>
+        <v>146</v>
       </c>
       <c r="L18" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>419</v>
       </c>
       <c r="N18" t="n">
-        <v>1261</v>
+        <v>3724</v>
       </c>
       <c r="O18" t="n">
-        <v>12.28</v>
+        <v>18.32</v>
       </c>
       <c r="P18" t="n">
-        <v>9.74</v>
+        <v>33.42</v>
       </c>
       <c r="Q18" t="n">
-        <v>9.59</v>
+        <v>33.58</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Divis Laboratories Ltd</t>
+          <t>Eicher Motors Ltd</t>
         </is>
       </c>
       <c r="S18" t="n">
-        <v>16.5</v>
+        <v>31.1</v>
       </c>
       <c r="T18" t="n">
-        <v>1615028.67</v>
+        <v>222391.83</v>
       </c>
       <c r="U18" t="n">
-        <v>69.95</v>
+        <v>15.62</v>
       </c>
       <c r="V18" t="n">
-        <v>12.34</v>
+        <v>13.61</v>
       </c>
       <c r="W18" t="n">
-        <v>1.39</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -6738,75 +8190,75 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4.99</v>
+        <v>7.43</v>
       </c>
       <c r="D19" t="n">
-        <v>8.08</v>
+        <v>10.74</v>
       </c>
       <c r="E19" t="n">
-        <v>13.56</v>
+        <v>12.86</v>
       </c>
       <c r="F19" t="n">
-        <v>0.03</v>
+        <v>0.28</v>
       </c>
       <c r="G19" t="n">
-        <v>73.29000000000001</v>
+        <v>23.62</v>
       </c>
       <c r="H19" t="n">
-        <v>2.4</v>
+        <v>1.07</v>
       </c>
       <c r="I19" t="n">
-        <v>5214</v>
+        <v>20812</v>
       </c>
       <c r="J19" t="n">
-        <v>2468</v>
+        <v>8226</v>
       </c>
       <c r="K19" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M19" t="n">
-        <v>592</v>
+        <v>21794</v>
       </c>
       <c r="N19" t="n">
-        <v>2746</v>
+        <v>12586</v>
       </c>
       <c r="O19" t="n">
-        <v>26.71</v>
+        <v>24.1</v>
       </c>
       <c r="P19" t="n">
-        <v>32.37</v>
+        <v>17.08</v>
       </c>
       <c r="Q19" t="n">
-        <v>28.88</v>
+        <v>18.92</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Avenue Supermarts Ltd</t>
+          <t>GAIL (India) Ltd</t>
         </is>
       </c>
       <c r="S19" t="n">
-        <v>19.4</v>
+        <v>14.7</v>
       </c>
       <c r="T19" t="n">
-        <v>3053088.97</v>
+        <v>1531867.57</v>
       </c>
       <c r="U19" t="n">
-        <v>72.53</v>
+        <v>25.84</v>
       </c>
       <c r="V19" t="n">
-        <v>11.71</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>1.94</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -6815,75 +8267,75 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>19.91</v>
+        <v>7.58</v>
       </c>
       <c r="D20" t="n">
-        <v>28.32</v>
+        <v>20.76</v>
       </c>
       <c r="E20" t="n">
-        <v>19.74</v>
+        <v>11.2</v>
       </c>
       <c r="F20" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.55</v>
       </c>
       <c r="G20" t="n">
-        <v>51.71</v>
+        <v>3.02</v>
       </c>
       <c r="H20" t="n">
-        <v>0.72</v>
+        <v>0.32</v>
       </c>
       <c r="I20" t="n">
-        <v>8577</v>
+        <v>12395</v>
       </c>
       <c r="J20" t="n">
-        <v>4034</v>
+        <v>23114</v>
       </c>
       <c r="K20" t="n">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="L20" t="n">
         <v>12</v>
       </c>
       <c r="M20" t="n">
-        <v>2002</v>
+        <v>137155</v>
       </c>
       <c r="N20" t="n">
-        <v>4543</v>
+        <v>-10719</v>
       </c>
       <c r="O20" t="n">
-        <v>8.42</v>
+        <v>15.74</v>
       </c>
       <c r="P20" t="n">
-        <v>11.18</v>
+        <v>5.61</v>
       </c>
       <c r="Q20" t="n">
-        <v>11.15</v>
+        <v>1.55</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Dr Reddys Laboratories Ltd</t>
+          <t>Grasim Industries Ltd</t>
         </is>
       </c>
       <c r="S20" t="n">
-        <v>26.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>2441803.28</v>
+        <v>478951.82</v>
       </c>
       <c r="U20" t="n">
-        <v>11.73</v>
+        <v>79.34999999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>10.19</v>
+        <v>5.68</v>
       </c>
       <c r="W20" t="n">
-        <v>0.09</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -6892,75 +8344,75 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24.2</v>
+        <v>25</v>
       </c>
       <c r="D21" t="n">
-        <v>26.18</v>
+        <v>32.09</v>
       </c>
       <c r="E21" t="n">
-        <v>22.17</v>
+        <v>3816.58</v>
       </c>
       <c r="F21" t="n">
-        <v>0.02</v>
+        <v>0.62</v>
       </c>
       <c r="G21" t="n">
-        <v>114.71</v>
+        <v>270.88</v>
       </c>
       <c r="H21" t="n">
-        <v>0.72</v>
+        <v>67.51000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>6558</v>
+        <v>14638</v>
       </c>
       <c r="J21" t="n">
-        <v>2834</v>
+        <v>6412</v>
       </c>
       <c r="K21" t="n">
-        <v>146</v>
+        <v>114</v>
       </c>
       <c r="L21" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="M21" t="n">
-        <v>419</v>
+        <v>123</v>
       </c>
       <c r="N21" t="n">
-        <v>3724</v>
+        <v>8226</v>
       </c>
       <c r="O21" t="n">
-        <v>8.539999999999999</v>
+        <v>8.02</v>
       </c>
       <c r="P21" t="n">
-        <v>20.08</v>
+        <v>27.17</v>
       </c>
       <c r="Q21" t="n">
-        <v>23.83</v>
+        <v>27.54</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Eicher Motors Ltd</t>
+          <t>Hindustan Aeronautics Ltd</t>
         </is>
       </c>
       <c r="S21" t="n">
-        <v>31.1</v>
+        <v>38.9</v>
       </c>
       <c r="T21" t="n">
-        <v>222391.83</v>
+        <v>2643616.86</v>
       </c>
       <c r="U21" t="n">
-        <v>15.62</v>
+        <v>71.89</v>
       </c>
       <c r="V21" t="n">
-        <v>13.61</v>
+        <v>3.65</v>
       </c>
       <c r="W21" t="n">
-        <v>4.41</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>HAVELLS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -6969,152 +8421,152 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>7.43</v>
+        <v>6.84</v>
       </c>
       <c r="D22" t="n">
-        <v>10.74</v>
+        <v>10.12</v>
       </c>
       <c r="E22" t="n">
-        <v>12.86</v>
+        <v>17.07</v>
       </c>
       <c r="F22" t="n">
-        <v>0.28</v>
+        <v>0.04</v>
       </c>
       <c r="G22" t="n">
-        <v>23.62</v>
+        <v>25.36</v>
       </c>
       <c r="H22" t="n">
-        <v>1.07</v>
+        <v>1.5</v>
       </c>
       <c r="I22" t="n">
-        <v>20812</v>
+        <v>3571</v>
       </c>
       <c r="J22" t="n">
-        <v>8226</v>
+        <v>1618</v>
       </c>
       <c r="K22" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L22" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="M22" t="n">
-        <v>21794</v>
+        <v>303</v>
       </c>
       <c r="N22" t="n">
-        <v>12586</v>
+        <v>1953</v>
       </c>
       <c r="O22" t="n">
-        <v>8.529999999999999</v>
+        <v>18.58</v>
       </c>
       <c r="P22" t="n">
-        <v>8.44</v>
+        <v>7.61</v>
       </c>
       <c r="Q22" t="n">
-        <v>9.59</v>
+        <v>6.66</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>GAIL (India) Ltd</t>
+          <t>Havells India Ltd</t>
         </is>
       </c>
       <c r="S22" t="n">
-        <v>14.7</v>
+        <v>24.4</v>
       </c>
       <c r="T22" t="n">
-        <v>1531867.57</v>
+        <v>2521508.87</v>
       </c>
       <c r="U22" t="n">
-        <v>25.84</v>
+        <v>45.41</v>
       </c>
       <c r="V22" t="n">
-        <v>9.539999999999999</v>
+        <v>14.08</v>
       </c>
       <c r="W22" t="n">
-        <v>0.31</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>Jun 2015</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7.58</v>
+        <v>20</v>
       </c>
       <c r="D23" t="n">
-        <v>20.76</v>
+        <v>23.12</v>
       </c>
       <c r="E23" t="n">
-        <v>11.2</v>
+        <v>30.31</v>
       </c>
       <c r="F23" t="n">
-        <v>1.55</v>
+        <v>0.03</v>
       </c>
       <c r="G23" t="n">
-        <v>3.02</v>
+        <v>105.63</v>
       </c>
       <c r="H23" t="n">
-        <v>0.32</v>
+        <v>1.04</v>
       </c>
       <c r="I23" t="n">
-        <v>12395</v>
+        <v>7627</v>
       </c>
       <c r="J23" t="n">
-        <v>23114</v>
+        <v>2088</v>
       </c>
       <c r="K23" t="n">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="L23" t="n">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="M23" t="n">
-        <v>137155</v>
+        <v>648</v>
       </c>
       <c r="N23" t="n">
-        <v>-10719</v>
+        <v>5539</v>
       </c>
       <c r="O23" t="n">
-        <v>14.19</v>
+        <v>38.72</v>
       </c>
       <c r="P23" t="n">
-        <v>7.19</v>
+        <v>32.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.36</v>
+        <v>33.22</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Grasim Industries Ltd</t>
+          <t>HCL Technologies Ltd</t>
         </is>
       </c>
       <c r="S23" t="n">
-        <v>9.300000000000001</v>
+        <v>29.6</v>
       </c>
       <c r="T23" t="n">
-        <v>478951.82</v>
+        <v>412593.29</v>
       </c>
       <c r="U23" t="n">
-        <v>79.34999999999999</v>
+        <v>63.63</v>
       </c>
       <c r="V23" t="n">
-        <v>5.68</v>
+        <v>5.44</v>
       </c>
       <c r="W23" t="n">
-        <v>0.98</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -7123,75 +8575,75 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>25</v>
+        <v>1.55</v>
       </c>
       <c r="D24" t="n">
-        <v>32.09</v>
+        <v>99.48</v>
       </c>
       <c r="E24" t="n">
-        <v>3816.58</v>
+        <v>10.73</v>
       </c>
       <c r="F24" t="n">
-        <v>0.62</v>
+        <v>0.06</v>
       </c>
       <c r="G24" t="n">
-        <v>270.88</v>
+        <v>192.29</v>
       </c>
       <c r="H24" t="n">
-        <v>67.51000000000001</v>
+        <v>0.34</v>
       </c>
       <c r="I24" t="n">
-        <v>14638</v>
+        <v>24335</v>
       </c>
       <c r="J24" t="n">
-        <v>6412</v>
+        <v>13614</v>
       </c>
       <c r="K24" t="n">
-        <v>114</v>
+        <v>7</v>
       </c>
       <c r="L24" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="M24" t="n">
-        <v>123</v>
+        <v>950</v>
       </c>
       <c r="N24" t="n">
-        <v>8226</v>
+        <v>10721</v>
       </c>
       <c r="O24" t="n">
-        <v>6.69</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>9.050000000000001</v>
+        <v>6.44</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.2</v>
+        <v>3.39</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Hindustan Aeronautics Ltd</t>
+          <t>HDFC Life Insurance Company Ltd</t>
         </is>
       </c>
       <c r="S24" t="n">
-        <v>38.9</v>
+        <v>6.61</v>
       </c>
       <c r="T24" t="n">
-        <v>2643616.86</v>
+        <v>47027.6</v>
       </c>
       <c r="U24" t="n">
-        <v>71.89</v>
+        <v>50.59</v>
       </c>
       <c r="V24" t="n">
-        <v>3.65</v>
+        <v>11.28</v>
       </c>
       <c r="W24" t="n">
-        <v>2.77</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -7200,152 +8652,153 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6.84</v>
+        <v>9.9</v>
       </c>
       <c r="D25" t="n">
-        <v>10.12</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>17.07</v>
+        <v>21.14</v>
       </c>
       <c r="F25" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="G25" t="n">
-        <v>25.36</v>
+        <v>47.27</v>
       </c>
       <c r="H25" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="I25" t="n">
-        <v>3571</v>
+        <v>6751</v>
       </c>
       <c r="J25" t="n">
-        <v>1618</v>
+        <v>1828</v>
       </c>
       <c r="K25" t="n">
-        <v>20</v>
+        <v>187</v>
       </c>
       <c r="L25" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="M25" t="n">
-        <v>303</v>
+        <v>606</v>
       </c>
       <c r="N25" t="n">
-        <v>1953</v>
+        <v>4923</v>
       </c>
       <c r="O25" t="n">
-        <v>9.27</v>
+        <v>6.68</v>
       </c>
       <c r="P25" t="n">
-        <v>7.6</v>
+        <v>8.92</v>
       </c>
       <c r="Q25" t="n">
-        <v>7.73</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Havells India Ltd</t>
+          <t xml:space="preserve">Hero MotoCorp Ltd
+</t>
         </is>
       </c>
       <c r="S25" t="n">
-        <v>24.4</v>
+        <v>29.1</v>
       </c>
       <c r="T25" t="n">
-        <v>2521508.87</v>
+        <v>1593400.88</v>
       </c>
       <c r="U25" t="n">
-        <v>45.41</v>
+        <v>53.86</v>
       </c>
       <c r="V25" t="n">
-        <v>14.08</v>
+        <v>12.6</v>
       </c>
       <c r="W25" t="n">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Jun 2015</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>20</v>
+        <v>4.7</v>
       </c>
       <c r="D26" t="n">
-        <v>23.12</v>
+        <v>88.95</v>
       </c>
       <c r="E26" t="n">
-        <v>30.31</v>
+        <v>9.57</v>
       </c>
       <c r="F26" t="n">
-        <v>0.03</v>
+        <v>0.53</v>
       </c>
       <c r="G26" t="n">
-        <v>105.63</v>
+        <v>126.47</v>
       </c>
       <c r="H26" t="n">
-        <v>1.04</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>7627</v>
+        <v>38323</v>
       </c>
       <c r="J26" t="n">
-        <v>2088</v>
+        <v>14267</v>
       </c>
       <c r="K26" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="L26" t="n">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="M26" t="n">
-        <v>648</v>
+        <v>56356</v>
       </c>
       <c r="N26" t="n">
-        <v>5539</v>
+        <v>24056</v>
       </c>
       <c r="O26" t="n">
-        <v>7.66</v>
+        <v>14.14</v>
       </c>
       <c r="P26" t="n">
-        <v>5.88</v>
+        <v>37.61</v>
       </c>
       <c r="Q26" t="n">
-        <v>6.38</v>
+        <v>36.78</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>HCL Technologies Ltd</t>
+          <t>Hindalco Industries Ltd</t>
         </is>
       </c>
       <c r="S26" t="n">
-        <v>29.6</v>
+        <v>11.3</v>
       </c>
       <c r="T26" t="n">
-        <v>412593.29</v>
+        <v>722281.1</v>
       </c>
       <c r="U26" t="n">
-        <v>63.63</v>
+        <v>56.45</v>
       </c>
       <c r="V26" t="n">
-        <v>5.44</v>
+        <v>9.32</v>
       </c>
       <c r="W26" t="n">
-        <v>1.99</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -7354,75 +8807,76 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.55</v>
+        <v>16.61</v>
       </c>
       <c r="D27" t="n">
-        <v>99.48</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>10.73</v>
+        <v>20.07</v>
       </c>
       <c r="F27" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G27" t="n">
-        <v>192.29</v>
+        <v>57.85</v>
       </c>
       <c r="H27" t="n">
-        <v>0.34</v>
+        <v>0.79</v>
       </c>
       <c r="I27" t="n">
-        <v>24335</v>
+        <v>20793</v>
       </c>
       <c r="J27" t="n">
-        <v>13614</v>
+        <v>5324</v>
       </c>
       <c r="K27" t="n">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="L27" t="n">
-        <v>27</v>
+        <v>96</v>
       </c>
       <c r="M27" t="n">
-        <v>950</v>
+        <v>1484</v>
       </c>
       <c r="N27" t="n">
-        <v>10721</v>
+        <v>15469</v>
       </c>
       <c r="O27" t="n">
-        <v>17.84</v>
+        <v>7.44</v>
       </c>
       <c r="P27" t="n">
-        <v>12.03</v>
+        <v>7.69</v>
       </c>
       <c r="Q27" t="n">
-        <v>12.25</v>
+        <v>7.85</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>HDFC Life Insurance Company Ltd</t>
+          <t xml:space="preserve">Hindustan Unilever Ltd
+</t>
         </is>
       </c>
       <c r="S27" t="n">
-        <v>6.61</v>
+        <v>27.2</v>
       </c>
       <c r="T27" t="n">
-        <v>47027.6</v>
+        <v>548890.59</v>
       </c>
       <c r="U27" t="n">
-        <v>50.59</v>
+        <v>34.51</v>
       </c>
       <c r="V27" t="n">
-        <v>11.28</v>
+        <v>11.88</v>
       </c>
       <c r="W27" t="n">
-        <v>3.22</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>ICICIGI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7431,75 +8885,75 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4.7</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>88.95</v>
+        <v>87.42</v>
       </c>
       <c r="E28" t="n">
-        <v>9.57</v>
+        <v>15.72</v>
       </c>
       <c r="F28" t="n">
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>126.47</v>
+        <v>160.03</v>
       </c>
       <c r="H28" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.32</v>
       </c>
       <c r="I28" t="n">
-        <v>38323</v>
+        <v>4328</v>
       </c>
       <c r="J28" t="n">
-        <v>14267</v>
+        <v>1921</v>
       </c>
       <c r="K28" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="L28" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="M28" t="n">
-        <v>56356</v>
+        <v>35</v>
       </c>
       <c r="N28" t="n">
-        <v>24056</v>
+        <v>2407</v>
       </c>
       <c r="O28" t="n">
-        <v>8.94</v>
+        <v>17.65</v>
       </c>
       <c r="P28" t="n">
-        <v>12.6</v>
+        <v>14.34</v>
       </c>
       <c r="Q28" t="n">
-        <v>11</v>
+        <v>12.36</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Hindalco Industries Ltd</t>
+          <t>ICICI Lombard General Insurance Company Ltd</t>
         </is>
       </c>
       <c r="S28" t="n">
-        <v>11.3</v>
+        <v>22.5</v>
       </c>
       <c r="T28" t="n">
-        <v>722281.1</v>
+        <v>1271789.21</v>
       </c>
       <c r="U28" t="n">
-        <v>56.45</v>
+        <v>49</v>
       </c>
       <c r="V28" t="n">
-        <v>9.32</v>
+        <v>7.86</v>
       </c>
       <c r="W28" t="n">
-        <v>0.98</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -7508,76 +8962,75 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>16.61</v>
+        <v>17.08</v>
       </c>
       <c r="D29" t="n">
-        <v>76.31999999999999</v>
+        <v>23.7</v>
       </c>
       <c r="E29" t="n">
-        <v>20.07</v>
+        <v>29.79</v>
       </c>
       <c r="F29" t="n">
-        <v>0.03</v>
+        <v>0.09</v>
       </c>
       <c r="G29" t="n">
-        <v>57.85</v>
+        <v>87.52</v>
       </c>
       <c r="H29" t="n">
-        <v>0.79</v>
+        <v>1.13</v>
       </c>
       <c r="I29" t="n">
-        <v>20793</v>
+        <v>30303</v>
       </c>
       <c r="J29" t="n">
-        <v>5324</v>
+        <v>5093</v>
       </c>
       <c r="K29" t="n">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="L29" t="n">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="M29" t="n">
-        <v>1484</v>
+        <v>8359</v>
       </c>
       <c r="N29" t="n">
-        <v>15469</v>
+        <v>25210</v>
       </c>
       <c r="O29" t="n">
-        <v>7.27</v>
+        <v>12.33</v>
       </c>
       <c r="P29" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>10.46</v>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Infosys Ltd</t>
+        </is>
+      </c>
+      <c r="S29" t="n">
+        <v>40</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1112279.92</v>
+      </c>
+      <c r="U29" t="n">
+        <v>35.99</v>
+      </c>
+      <c r="V29" t="n">
         <v>8.970000000000001</v>
       </c>
-      <c r="Q29" t="n">
-        <v>8.130000000000001</v>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hindustan Unilever Ltd
-</t>
-        </is>
-      </c>
-      <c r="S29" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="T29" t="n">
-        <v>548890.59</v>
-      </c>
-      <c r="U29" t="n">
-        <v>34.51</v>
-      </c>
-      <c r="V29" t="n">
-        <v>11.88</v>
-      </c>
       <c r="W29" t="n">
-        <v>4.32</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7586,75 +9039,75 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>9.369999999999999</v>
+        <v>26.02</v>
       </c>
       <c r="D30" t="n">
-        <v>87.42</v>
+        <v>34.33</v>
       </c>
       <c r="E30" t="n">
-        <v>15.72</v>
+        <v>34.4</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="G30" t="n">
-        <v>160.03</v>
+        <v>82.73999999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>0.32</v>
+        <v>0.7</v>
       </c>
       <c r="I30" t="n">
-        <v>4328</v>
+        <v>1097</v>
       </c>
       <c r="J30" t="n">
-        <v>1921</v>
+        <v>215</v>
       </c>
       <c r="K30" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="L30" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="M30" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="N30" t="n">
-        <v>2407</v>
+        <v>882</v>
       </c>
       <c r="O30" t="n">
-        <v>15.79</v>
+        <v>54.74</v>
       </c>
       <c r="P30" t="n">
-        <v>17.79</v>
+        <v>59.16</v>
       </c>
       <c r="Q30" t="n">
-        <v>16.69</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>ICICI Lombard General Insurance Company Ltd</t>
+          <t>Indian Railway Catering &amp; Tourism Corporation Ltd</t>
         </is>
       </c>
       <c r="S30" t="n">
-        <v>22.5</v>
+        <v>53.8</v>
       </c>
       <c r="T30" t="n">
-        <v>1271789.21</v>
+        <v>1258520.29</v>
       </c>
       <c r="U30" t="n">
-        <v>49</v>
+        <v>60.44</v>
       </c>
       <c r="V30" t="n">
-        <v>7.86</v>
+        <v>5.74</v>
       </c>
       <c r="W30" t="n">
-        <v>3.46</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -7663,75 +9116,76 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>11.85</v>
+        <v>29.28</v>
       </c>
       <c r="D31" t="n">
-        <v>76.3</v>
+        <v>37.02</v>
       </c>
       <c r="E31" t="n">
-        <v>892.5700000000001</v>
+        <v>27.85</v>
       </c>
       <c r="F31" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>22.61</v>
+        <v>362.96</v>
       </c>
       <c r="H31" t="n">
-        <v>56.39</v>
+        <v>0.77</v>
       </c>
       <c r="I31" t="n">
-        <v>32942</v>
+        <v>18742</v>
       </c>
       <c r="J31" t="n">
-        <v>11759</v>
+        <v>1563</v>
       </c>
       <c r="K31" t="n">
-        <v>212</v>
+        <v>16</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="M31" t="n">
-        <v>17</v>
+        <v>303</v>
       </c>
       <c r="N31" t="n">
-        <v>21183</v>
+        <v>17179</v>
       </c>
       <c r="O31" t="n">
-        <v>19.3</v>
+        <v>11.13</v>
       </c>
       <c r="P31" t="n">
-        <v>18.57</v>
+        <v>11.69</v>
       </c>
       <c r="Q31" t="n">
-        <v>-34.6</v>
+        <v>9.82</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>Interglobe Aviation Ltd</t>
+          <t xml:space="preserve">ITC Ltd
+</t>
         </is>
       </c>
       <c r="S31" t="n">
-        <v>24.5</v>
+        <v>34.76</v>
       </c>
       <c r="T31" t="n">
-        <v>1040632.92</v>
+        <v>332245.58</v>
       </c>
       <c r="U31" t="n">
-        <v>76.23</v>
+        <v>47.85</v>
       </c>
       <c r="V31" t="n">
-        <v>7.87</v>
+        <v>3.24</v>
       </c>
       <c r="W31" t="n">
-        <v>4.27</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -7740,75 +9194,75 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>17.08</v>
+        <v>15.02</v>
       </c>
       <c r="D32" t="n">
-        <v>23.7</v>
+        <v>46.86</v>
       </c>
       <c r="E32" t="n">
-        <v>29.79</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>0.09</v>
+        <v>1.52</v>
       </c>
       <c r="G32" t="n">
-        <v>87.52</v>
+        <v>2.85</v>
       </c>
       <c r="H32" t="n">
-        <v>1.13</v>
+        <v>0.2</v>
       </c>
       <c r="I32" t="n">
-        <v>30303</v>
+        <v>14431</v>
       </c>
       <c r="J32" t="n">
-        <v>5093</v>
+        <v>8197</v>
       </c>
       <c r="K32" t="n">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="L32" t="n">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="M32" t="n">
-        <v>8359</v>
+        <v>31573</v>
       </c>
       <c r="N32" t="n">
-        <v>25210</v>
+        <v>6234</v>
       </c>
       <c r="O32" t="n">
-        <v>12.16</v>
+        <v>13.32</v>
       </c>
       <c r="P32" t="n">
-        <v>9.390000000000001</v>
+        <v>24.67</v>
       </c>
       <c r="Q32" t="n">
-        <v>10.15</v>
+        <v>21.79</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>Infosys Ltd</t>
+          <t>JSW Energy Ltd</t>
         </is>
       </c>
       <c r="S32" t="n">
-        <v>40</v>
+        <v>8.59</v>
       </c>
       <c r="T32" t="n">
-        <v>1112279.92</v>
+        <v>110870.53</v>
       </c>
       <c r="U32" t="n">
-        <v>35.99</v>
+        <v>24.79</v>
       </c>
       <c r="V32" t="n">
-        <v>8.970000000000001</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="W32" t="n">
-        <v>4.1</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -7817,75 +9271,73 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>26.02</v>
+        <v>4.84</v>
       </c>
       <c r="D33" t="n">
-        <v>34.33</v>
+        <v>3.87</v>
       </c>
       <c r="E33" t="n">
-        <v>34.4</v>
+        <v>49.45</v>
       </c>
       <c r="F33" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>82.73999999999999</v>
+        <v>371.94</v>
       </c>
       <c r="H33" t="n">
-        <v>0.7</v>
+        <v>0.16</v>
       </c>
       <c r="I33" t="n">
-        <v>1097</v>
+        <v>51391</v>
       </c>
       <c r="J33" t="n">
-        <v>215</v>
+        <v>25269</v>
       </c>
       <c r="K33" t="n">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="L33" t="n">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="M33" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>882</v>
+        <v>26122</v>
       </c>
       <c r="O33" t="n">
-        <v>15.45</v>
+        <v>6.72</v>
       </c>
       <c r="P33" t="n">
-        <v>24.79</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1.44</v>
-      </c>
+        <v>93.23999999999999</v>
+      </c>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
-          <t>Indian Railway Catering &amp; Tourism Corporation Ltd</t>
+          <t>Life Insurance Corporation of India</t>
         </is>
       </c>
       <c r="S33" t="n">
-        <v>53.8</v>
+        <v>63.79</v>
       </c>
       <c r="T33" t="n">
-        <v>1258520.29</v>
+        <v>183583.67</v>
       </c>
       <c r="U33" t="n">
-        <v>60.44</v>
+        <v>30.67</v>
       </c>
       <c r="V33" t="n">
-        <v>5.74</v>
+        <v>8.1</v>
       </c>
       <c r="W33" t="n">
-        <v>1.08</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>LODHA</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -7894,76 +9346,75 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>29.28</v>
+        <v>15.06</v>
       </c>
       <c r="D34" t="n">
-        <v>37.02</v>
+        <v>25.83</v>
       </c>
       <c r="E34" t="n">
-        <v>27.85</v>
+        <v>8.9</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="G34" t="n">
-        <v>362.96</v>
+        <v>5.63</v>
       </c>
       <c r="H34" t="n">
-        <v>0.77</v>
+        <v>0.22</v>
       </c>
       <c r="I34" t="n">
-        <v>18742</v>
+        <v>5459</v>
       </c>
       <c r="J34" t="n">
-        <v>1563</v>
+        <v>2947</v>
       </c>
       <c r="K34" t="n">
         <v>16</v>
       </c>
       <c r="L34" t="n">
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="M34" t="n">
-        <v>303</v>
+        <v>7698</v>
       </c>
       <c r="N34" t="n">
-        <v>17179</v>
+        <v>2512</v>
       </c>
       <c r="O34" t="n">
-        <v>7.48</v>
+        <v>25.63</v>
       </c>
       <c r="P34" t="n">
-        <v>8.640000000000001</v>
+        <v>168.94</v>
       </c>
       <c r="Q34" t="n">
-        <v>8.52</v>
+        <v>123.61</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITC Ltd
-</t>
+          <t>Macrotech Developers Ltd</t>
         </is>
       </c>
       <c r="S34" t="n">
-        <v>34.76</v>
+        <v>11.1</v>
       </c>
       <c r="T34" t="n">
-        <v>332245.58</v>
+        <v>1209919.99</v>
       </c>
       <c r="U34" t="n">
-        <v>47.85</v>
+        <v>51.95</v>
       </c>
       <c r="V34" t="n">
-        <v>3.24</v>
+        <v>7.65</v>
       </c>
       <c r="W34" t="n">
-        <v>4.26</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7972,73 +9423,75 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>86.52</v>
+        <v>7.03</v>
       </c>
       <c r="D35" t="n">
-        <v>84.04000000000001</v>
+        <v>13.51</v>
       </c>
       <c r="E35" t="n">
-        <v>1.15</v>
+        <v>77.67</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G35" t="n">
-        <v>198.8</v>
+        <v>3.54</v>
       </c>
       <c r="H35" t="n">
-        <v>0.01</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>763</v>
+        <v>20445</v>
       </c>
       <c r="J35" t="n">
-        <v>1441</v>
+        <v>2179</v>
       </c>
       <c r="K35" t="n">
-        <v>3</v>
+        <v>95</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>2071</v>
       </c>
       <c r="N35" t="n">
-        <v>-678</v>
+        <v>18266</v>
       </c>
       <c r="O35" t="n">
-        <v>561.3099999999999</v>
+        <v>15.13</v>
       </c>
       <c r="P35" t="n">
-        <v>619.99</v>
-      </c>
-      <c r="Q35" t="inlineStr"/>
+        <v>5.74</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>4.56</v>
+      </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>Jio Financial Services Ltd</t>
+          <t>Larsen &amp; Toubro Ltd</t>
         </is>
       </c>
       <c r="S35" t="n">
-        <v>2.16</v>
+        <v>17.18</v>
       </c>
       <c r="T35" t="n">
-        <v>1401774.99</v>
+        <v>1124597.5</v>
       </c>
       <c r="U35" t="n">
-        <v>34.24</v>
+        <v>30.8</v>
       </c>
       <c r="V35" t="n">
-        <v>9.91</v>
+        <v>2.48</v>
       </c>
       <c r="W35" t="n">
-        <v>3.09</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>LTIM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -8047,75 +9500,75 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5.13</v>
+        <v>12.91</v>
       </c>
       <c r="D36" t="n">
-        <v>16.09</v>
+        <v>17.98</v>
       </c>
       <c r="E36" t="n">
-        <v>11.55</v>
+        <v>22.9</v>
       </c>
       <c r="F36" t="n">
-        <v>1.13</v>
+        <v>0.1</v>
       </c>
       <c r="G36" t="n">
-        <v>3.66</v>
+        <v>31.93</v>
       </c>
       <c r="H36" t="n">
-        <v>0.77</v>
+        <v>1.29</v>
       </c>
       <c r="I36" t="n">
-        <v>26545</v>
+        <v>9588</v>
       </c>
       <c r="J36" t="n">
-        <v>14467</v>
+        <v>3918</v>
       </c>
       <c r="K36" t="n">
-        <v>36</v>
+        <v>155</v>
       </c>
       <c r="L36" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="M36" t="n">
-        <v>87984</v>
+        <v>2071</v>
       </c>
       <c r="N36" t="n">
-        <v>12078</v>
+        <v>5670</v>
       </c>
       <c r="O36" t="n">
-        <v>13.26</v>
+        <v>31.62</v>
       </c>
       <c r="P36" t="n">
-        <v>11.17</v>
+        <v>23.95</v>
       </c>
       <c r="Q36" t="n">
-        <v>11</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>JSW Steel Ltd</t>
+          <t>LTIMindtree Ltd</t>
         </is>
       </c>
       <c r="S36" t="n">
-        <v>13.36</v>
+        <v>34.1</v>
       </c>
       <c r="T36" t="n">
-        <v>2612646.38</v>
+        <v>1347046.9</v>
       </c>
       <c r="U36" t="n">
-        <v>69.27</v>
+        <v>64.52</v>
       </c>
       <c r="V36" t="n">
-        <v>4.37</v>
+        <v>2.38</v>
       </c>
       <c r="W36" t="n">
-        <v>2.94</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -8124,73 +9577,75 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4.84</v>
+        <v>9.51</v>
       </c>
       <c r="D37" t="n">
-        <v>3.87</v>
+        <v>13.13</v>
       </c>
       <c r="E37" t="n">
-        <v>49.45</v>
+        <v>15.75</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>371.94</v>
+        <v>117.91</v>
       </c>
       <c r="H37" t="n">
-        <v>0.16</v>
+        <v>1.23</v>
       </c>
       <c r="I37" t="n">
-        <v>51391</v>
+        <v>28666</v>
       </c>
       <c r="J37" t="n">
-        <v>25269</v>
+        <v>11865</v>
       </c>
       <c r="K37" t="n">
-        <v>66</v>
+        <v>429</v>
       </c>
       <c r="L37" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="N37" t="n">
-        <v>26122</v>
+        <v>16801</v>
       </c>
       <c r="O37" t="n">
-        <v>7.78</v>
+        <v>19.85</v>
       </c>
       <c r="P37" t="n">
-        <v>58.38</v>
-      </c>
-      <c r="Q37" t="inlineStr"/>
+        <v>33.69</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>32.43</v>
+      </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>Life Insurance Corporation of India</t>
+          <t>Maruti Suzuki India Ltd</t>
         </is>
       </c>
       <c r="S37" t="n">
-        <v>63.79</v>
+        <v>23.67</v>
       </c>
       <c r="T37" t="n">
-        <v>183583.67</v>
+        <v>1503863.63</v>
       </c>
       <c r="U37" t="n">
-        <v>30.67</v>
+        <v>20.78</v>
       </c>
       <c r="V37" t="n">
-        <v>8.1</v>
+        <v>8.26</v>
       </c>
       <c r="W37" t="n">
-        <v>3.77</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>LODHA</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -8199,75 +9654,75 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>15.06</v>
+        <v>3.06</v>
       </c>
       <c r="D38" t="n">
-        <v>25.83</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="E38" t="n">
-        <v>8.9</v>
+        <v>11.55</v>
       </c>
       <c r="F38" t="n">
-        <v>0.44</v>
+        <v>0.76</v>
       </c>
       <c r="G38" t="n">
-        <v>5.63</v>
+        <v>5.22</v>
       </c>
       <c r="H38" t="n">
-        <v>0.22</v>
+        <v>1.17</v>
       </c>
       <c r="I38" t="n">
-        <v>5459</v>
+        <v>14213</v>
       </c>
       <c r="J38" t="n">
-        <v>2947</v>
+        <v>6644</v>
       </c>
       <c r="K38" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="L38" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="M38" t="n">
-        <v>7698</v>
+        <v>19922</v>
       </c>
       <c r="N38" t="n">
-        <v>2512</v>
+        <v>7569</v>
       </c>
       <c r="O38" t="n">
-        <v>16.49</v>
+        <v>17.51</v>
       </c>
       <c r="P38" t="n">
-        <v>20.65</v>
+        <v>27.32</v>
       </c>
       <c r="Q38" t="n">
-        <v>12.63</v>
+        <v>31.61</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>Macrotech Developers Ltd</t>
+          <t>Samvardhana Motherson International Ltd</t>
         </is>
       </c>
       <c r="S38" t="n">
-        <v>11.1</v>
+        <v>13.7</v>
       </c>
       <c r="T38" t="n">
-        <v>1209919.99</v>
+        <v>146151.16</v>
       </c>
       <c r="U38" t="n">
-        <v>51.95</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="V38" t="n">
-        <v>7.65</v>
+        <v>2.38</v>
       </c>
       <c r="W38" t="n">
-        <v>4.05</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -8276,75 +9731,75 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>7.03</v>
+        <v>16.12</v>
       </c>
       <c r="D39" t="n">
-        <v>13.51</v>
+        <v>23.83</v>
       </c>
       <c r="E39" t="n">
-        <v>77.67</v>
+        <v>117.75</v>
       </c>
       <c r="F39" t="n">
         <v>0.1</v>
       </c>
       <c r="G39" t="n">
-        <v>3.54</v>
+        <v>41.19</v>
       </c>
       <c r="H39" t="n">
-        <v>8.029999999999999</v>
+        <v>2.32</v>
       </c>
       <c r="I39" t="n">
-        <v>20445</v>
+        <v>5412</v>
       </c>
       <c r="J39" t="n">
-        <v>2179</v>
+        <v>1237</v>
       </c>
       <c r="K39" t="n">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="L39" t="n">
-        <v>36</v>
+        <v>79</v>
       </c>
       <c r="M39" t="n">
-        <v>2071</v>
+        <v>345</v>
       </c>
       <c r="N39" t="n">
-        <v>18266</v>
+        <v>4175</v>
       </c>
       <c r="O39" t="n">
-        <v>10.21</v>
+        <v>7.64</v>
       </c>
       <c r="P39" t="n">
-        <v>9.75</v>
+        <v>11.92</v>
       </c>
       <c r="Q39" t="n">
-        <v>8.210000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>Larsen &amp; Toubro Ltd</t>
+          <t>Nestle India Ltd</t>
         </is>
       </c>
       <c r="S39" t="n">
-        <v>17.18</v>
+        <v>185.43</v>
       </c>
       <c r="T39" t="n">
-        <v>1124597.5</v>
+        <v>1677775.19</v>
       </c>
       <c r="U39" t="n">
-        <v>30.8</v>
+        <v>54.96</v>
       </c>
       <c r="V39" t="n">
-        <v>2.48</v>
+        <v>14.34</v>
       </c>
       <c r="W39" t="n">
-        <v>1.26</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>LTIM</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -8353,75 +9808,75 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>12.91</v>
+        <v>11.95</v>
       </c>
       <c r="D40" t="n">
-        <v>17.98</v>
+        <v>28.83</v>
       </c>
       <c r="E40" t="n">
-        <v>22.9</v>
+        <v>13.27</v>
       </c>
       <c r="F40" t="n">
-        <v>0.1</v>
+        <v>1.48</v>
       </c>
       <c r="G40" t="n">
-        <v>31.93</v>
+        <v>4.6</v>
       </c>
       <c r="H40" t="n">
-        <v>1.29</v>
+        <v>0.37</v>
       </c>
       <c r="I40" t="n">
-        <v>9588</v>
+        <v>72926</v>
       </c>
       <c r="J40" t="n">
-        <v>3918</v>
+        <v>32141</v>
       </c>
       <c r="K40" t="n">
-        <v>155</v>
+        <v>21</v>
       </c>
       <c r="L40" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="M40" t="n">
-        <v>2071</v>
+        <v>237131</v>
       </c>
       <c r="N40" t="n">
-        <v>5670</v>
+        <v>40785</v>
       </c>
       <c r="O40" t="n">
-        <v>20.78</v>
+        <v>13.62</v>
       </c>
       <c r="P40" t="n">
-        <v>19.09</v>
+        <v>10.78</v>
       </c>
       <c r="Q40" t="n">
-        <v>-1.01</v>
+        <v>11.28</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>LTIMindtree Ltd</t>
+          <t>NTPC Ltd</t>
         </is>
       </c>
       <c r="S40" t="n">
-        <v>34.1</v>
+        <v>10.58</v>
       </c>
       <c r="T40" t="n">
-        <v>1347046.9</v>
+        <v>907823.11</v>
       </c>
       <c r="U40" t="n">
-        <v>64.52</v>
+        <v>30.8</v>
       </c>
       <c r="V40" t="n">
-        <v>2.38</v>
+        <v>5.24</v>
       </c>
       <c r="W40" t="n">
-        <v>4.43</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -8430,75 +9885,75 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>9.51</v>
+        <v>9.66</v>
       </c>
       <c r="D41" t="n">
-        <v>13.13</v>
+        <v>17.39</v>
       </c>
       <c r="E41" t="n">
-        <v>15.75</v>
+        <v>16.94</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="G41" t="n">
-        <v>117.91</v>
+        <v>11.36</v>
       </c>
       <c r="H41" t="n">
-        <v>1.23</v>
+        <v>0.83</v>
       </c>
       <c r="I41" t="n">
-        <v>28666</v>
+        <v>156466</v>
       </c>
       <c r="J41" t="n">
-        <v>11865</v>
+        <v>57203</v>
       </c>
       <c r="K41" t="n">
-        <v>429</v>
+        <v>39</v>
       </c>
       <c r="L41" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M41" t="n">
-        <v>119</v>
+        <v>153181</v>
       </c>
       <c r="N41" t="n">
-        <v>16801</v>
+        <v>99263</v>
       </c>
       <c r="O41" t="n">
-        <v>10.4</v>
+        <v>21.34</v>
       </c>
       <c r="P41" t="n">
-        <v>15.57</v>
+        <v>18.64</v>
       </c>
       <c r="Q41" t="n">
-        <v>15.16</v>
+        <v>26.22</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>Maruti Suzuki India Ltd</t>
+          <t>Oil &amp; Natural Gas Corpn Ltd</t>
         </is>
       </c>
       <c r="S41" t="n">
-        <v>23.67</v>
+        <v>19.71</v>
       </c>
       <c r="T41" t="n">
-        <v>1503863.63</v>
+        <v>390111.05</v>
       </c>
       <c r="U41" t="n">
-        <v>20.78</v>
+        <v>18.15</v>
       </c>
       <c r="V41" t="n">
-        <v>8.26</v>
+        <v>10.36</v>
       </c>
       <c r="W41" t="n">
-        <v>1.78</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -8507,75 +9962,75 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3.06</v>
+        <v>14.11</v>
       </c>
       <c r="D42" t="n">
-        <v>9.449999999999999</v>
+        <v>21.87</v>
       </c>
       <c r="E42" t="n">
-        <v>11.55</v>
+        <v>20.78</v>
       </c>
       <c r="F42" t="n">
-        <v>0.76</v>
+        <v>0.05</v>
       </c>
       <c r="G42" t="n">
-        <v>5.22</v>
+        <v>54.33</v>
       </c>
       <c r="H42" t="n">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="I42" t="n">
-        <v>14213</v>
+        <v>4493</v>
       </c>
       <c r="J42" t="n">
-        <v>6644</v>
+        <v>1769</v>
       </c>
       <c r="K42" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="L42" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="M42" t="n">
-        <v>19922</v>
+        <v>382</v>
       </c>
       <c r="N42" t="n">
-        <v>7569</v>
+        <v>2724</v>
       </c>
       <c r="O42" t="n">
-        <v>12.98</v>
+        <v>15.33</v>
       </c>
       <c r="P42" t="n">
-        <v>20.23</v>
+        <v>15.05</v>
       </c>
       <c r="Q42" t="n">
-        <v>16.1</v>
+        <v>14.64</v>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>Samvardhana Motherson International Ltd</t>
+          <t>Pidilite Industries Ltd</t>
         </is>
       </c>
       <c r="S42" t="n">
-        <v>13.7</v>
+        <v>29.7</v>
       </c>
       <c r="T42" t="n">
-        <v>146151.16</v>
+        <v>162274.18</v>
       </c>
       <c r="U42" t="n">
-        <v>9.539999999999999</v>
+        <v>36.12</v>
       </c>
       <c r="V42" t="n">
-        <v>2.38</v>
+        <v>12.3</v>
       </c>
       <c r="W42" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -8584,75 +10039,76 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>23.46</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="D43" t="n">
-        <v>28.04</v>
+        <v>18.07</v>
       </c>
       <c r="E43" t="n">
-        <v>1.97</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="F43" t="n">
-        <v>0.01</v>
+        <v>0.58</v>
       </c>
       <c r="G43" t="n">
-        <v>28.97</v>
+        <v>7.73</v>
       </c>
       <c r="H43" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="I43" t="n">
-        <v>1554</v>
+        <v>272369</v>
       </c>
       <c r="J43" t="n">
-        <v>852</v>
+        <v>113581</v>
       </c>
       <c r="K43" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="L43" t="n">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="M43" t="n">
-        <v>246</v>
+        <v>458991</v>
       </c>
       <c r="N43" t="n">
-        <v>702</v>
+        <v>158788</v>
       </c>
       <c r="O43" t="n">
-        <v>15.51</v>
+        <v>19.15</v>
       </c>
       <c r="P43" t="n">
-        <v>17.95</v>
+        <v>10.44</v>
       </c>
       <c r="Q43" t="n">
-        <v>13.35</v>
+        <v>6.94</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>Info Edge (India) Ltd</t>
+          <t xml:space="preserve">Reliance Industries Ltd
+</t>
         </is>
       </c>
       <c r="S43" t="n">
-        <v>3.65</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="T43" t="n">
-        <v>563824.4399999999</v>
+        <v>432472.71</v>
       </c>
       <c r="U43" t="n">
-        <v>32.88</v>
+        <v>58.34</v>
       </c>
       <c r="V43" t="n">
-        <v>8.33</v>
+        <v>3.25</v>
       </c>
       <c r="W43" t="n">
-        <v>4.29</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -8661,229 +10117,221 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>16.12</v>
+        <v>1.43</v>
       </c>
       <c r="D44" t="n">
-        <v>23.83</v>
+        <v>0.19</v>
       </c>
       <c r="E44" t="n">
-        <v>117.75</v>
+        <v>12.7</v>
       </c>
       <c r="F44" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>41.19</v>
+        <v>240.33</v>
       </c>
       <c r="H44" t="n">
-        <v>2.32</v>
+        <v>0.33</v>
       </c>
       <c r="I44" t="n">
-        <v>5412</v>
+        <v>60343</v>
       </c>
       <c r="J44" t="n">
-        <v>1237</v>
+        <v>31221</v>
       </c>
       <c r="K44" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="L44" t="n">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="M44" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>4175</v>
+        <v>29122</v>
       </c>
       <c r="O44" t="n">
-        <v>6.69</v>
+        <v>12.26</v>
       </c>
       <c r="P44" t="n">
-        <v>9.51</v>
+        <v>13.44</v>
       </c>
       <c r="Q44" t="n">
-        <v>9.07</v>
+        <v>12.47</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>Nestle India Ltd</t>
+          <t>SBI Life Insurance Company Ltd</t>
         </is>
       </c>
       <c r="S44" t="n">
-        <v>185.43</v>
+        <v>13.2</v>
       </c>
       <c r="T44" t="n">
-        <v>1677775.19</v>
+        <v>886097.71</v>
       </c>
       <c r="U44" t="n">
-        <v>54.96</v>
+        <v>69.98</v>
       </c>
       <c r="V44" t="n">
-        <v>14.34</v>
+        <v>9.48</v>
       </c>
       <c r="W44" t="n">
-        <v>3.85</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>Jun 2015</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>14.11</v>
+        <v>6.81</v>
       </c>
       <c r="D45" t="n">
-        <v>21.87</v>
+        <v>21.47</v>
       </c>
       <c r="E45" t="n">
-        <v>20.78</v>
+        <v>8.07</v>
       </c>
       <c r="F45" t="n">
-        <v>0.05</v>
+        <v>0.17</v>
       </c>
       <c r="G45" t="n">
-        <v>54.33</v>
+        <v>11.95</v>
       </c>
       <c r="H45" t="n">
-        <v>1.03</v>
+        <v>0.78</v>
       </c>
       <c r="I45" t="n">
-        <v>4493</v>
+        <v>2229</v>
       </c>
       <c r="J45" t="n">
-        <v>1769</v>
+        <v>990</v>
       </c>
       <c r="K45" t="n">
-        <v>34</v>
+        <v>122</v>
       </c>
       <c r="L45" t="n">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="M45" t="n">
-        <v>382</v>
+        <v>917</v>
       </c>
       <c r="N45" t="n">
-        <v>2724</v>
+        <v>1239</v>
       </c>
       <c r="O45" t="n">
-        <v>11.02</v>
+        <v>37.66</v>
       </c>
       <c r="P45" t="n">
-        <v>13.67</v>
+        <v>10.97</v>
       </c>
       <c r="Q45" t="n">
-        <v>13.87</v>
+        <v>9.99</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>Pidilite Industries Ltd</t>
+          <t>Shree Cement Ltd</t>
         </is>
       </c>
       <c r="S45" t="n">
-        <v>29.7</v>
+        <v>14.8</v>
       </c>
       <c r="T45" t="n">
-        <v>162274.18</v>
+        <v>3154358.33</v>
       </c>
       <c r="U45" t="n">
-        <v>36.12</v>
+        <v>25.87</v>
       </c>
       <c r="V45" t="n">
-        <v>12.3</v>
+        <v>1.21</v>
       </c>
       <c r="W45" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>Sep 2024</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>33.97</v>
+        <v>12.22</v>
       </c>
       <c r="D46" t="n">
-        <v>86.87</v>
+        <v>13.96</v>
       </c>
       <c r="E46" t="n">
-        <v>17.87</v>
+        <v>17.7</v>
       </c>
       <c r="F46" t="n">
-        <v>1.42</v>
+        <v>0.02</v>
       </c>
       <c r="G46" t="n">
-        <v>4.6</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="H46" t="n">
-        <v>0.18</v>
+        <v>0.88</v>
       </c>
       <c r="I46" t="n">
-        <v>50404</v>
+        <v>2172</v>
       </c>
       <c r="J46" t="n">
-        <v>13114</v>
+        <v>502</v>
       </c>
       <c r="K46" t="n">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="L46" t="n">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="M46" t="n">
-        <v>123516</v>
+        <v>279</v>
       </c>
       <c r="N46" t="n">
-        <v>37290</v>
+        <v>1670</v>
       </c>
       <c r="O46" t="n">
-        <v>11.01</v>
+        <v>22.28</v>
       </c>
       <c r="P46" t="n">
-        <v>11.37</v>
+        <v>37.11</v>
       </c>
       <c r="Q46" t="n">
-        <v>10.74</v>
+        <v>36.33</v>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>Power Grid Corporation of India Ltd</t>
+          <t>Siemens Ltd</t>
         </is>
       </c>
       <c r="S46" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="T46" t="n">
-        <v>372584.24</v>
-      </c>
-      <c r="U46" t="n">
-        <v>64.39</v>
-      </c>
-      <c r="V46" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="W46" t="n">
-        <v>3.09</v>
-      </c>
+        <v>25.6</v>
+      </c>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -8892,76 +10340,75 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>8.789999999999999</v>
+        <v>19.82</v>
       </c>
       <c r="D47" t="n">
-        <v>18.07</v>
+        <v>26.84</v>
       </c>
       <c r="E47" t="n">
-        <v>9.960000000000001</v>
+        <v>15.09</v>
       </c>
       <c r="F47" t="n">
-        <v>0.58</v>
+        <v>0.05</v>
       </c>
       <c r="G47" t="n">
-        <v>7.73</v>
+        <v>58.33</v>
       </c>
       <c r="H47" t="n">
-        <v>0.51</v>
+        <v>0.57</v>
       </c>
       <c r="I47" t="n">
-        <v>272369</v>
+        <v>12898</v>
       </c>
       <c r="J47" t="n">
-        <v>113581</v>
+        <v>763</v>
       </c>
       <c r="K47" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="L47" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="M47" t="n">
-        <v>458991</v>
+        <v>3274</v>
       </c>
       <c r="N47" t="n">
-        <v>158788</v>
+        <v>12135</v>
       </c>
       <c r="O47" t="n">
-        <v>7.47</v>
+        <v>10.7</v>
       </c>
       <c r="P47" t="n">
-        <v>11.83</v>
+        <v>48.73</v>
       </c>
       <c r="Q47" t="n">
-        <v>10.74</v>
+        <v>39.92</v>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reliance Industries Ltd
-</t>
+          <t>Sun Pharmaceuticals Industries Ltd</t>
         </is>
       </c>
       <c r="S47" t="n">
-        <v>9.609999999999999</v>
+        <v>17.3</v>
       </c>
       <c r="T47" t="n">
-        <v>432472.71</v>
+        <v>1339586.09</v>
       </c>
       <c r="U47" t="n">
-        <v>58.34</v>
+        <v>37.9</v>
       </c>
       <c r="V47" t="n">
-        <v>3.25</v>
+        <v>6.71</v>
       </c>
       <c r="W47" t="n">
-        <v>4.21</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -8970,142 +10417,153 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1.43</v>
+        <v>7.99</v>
       </c>
       <c r="D48" t="n">
-        <v>0.19</v>
+        <v>15.02</v>
       </c>
       <c r="E48" t="n">
-        <v>12.7</v>
+        <v>7.57</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="G48" t="n">
-        <v>240.33</v>
+        <v>25.32</v>
       </c>
       <c r="H48" t="n">
-        <v>0.33</v>
+        <v>0.55</v>
       </c>
       <c r="I48" t="n">
-        <v>60343</v>
+        <v>3848</v>
       </c>
       <c r="J48" t="n">
-        <v>31221</v>
+        <v>1911</v>
       </c>
       <c r="K48" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="L48" t="n">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3477</v>
       </c>
       <c r="N48" t="n">
-        <v>29122</v>
+        <v>1937</v>
       </c>
       <c r="O48" t="n">
-        <v>19.81</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="P48" t="n">
-        <v>11.83</v>
+        <v>5.91</v>
       </c>
       <c r="Q48" t="n">
-        <v>12.25</v>
+        <v>7.46</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>SBI Life Insurance Company Ltd</t>
+          <t>Tata Consumer Products Ltd</t>
         </is>
       </c>
       <c r="S48" t="n">
-        <v>13.2</v>
+        <v>10.6</v>
       </c>
       <c r="T48" t="n">
-        <v>886097.71</v>
+        <v>350543.35</v>
       </c>
       <c r="U48" t="n">
-        <v>69.98</v>
+        <v>54.79</v>
       </c>
       <c r="V48" t="n">
-        <v>9.48</v>
+        <v>7.14</v>
       </c>
       <c r="W48" t="n">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Sep 2024</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>12.22</v>
+        <v>6.97</v>
       </c>
       <c r="D49" t="n">
-        <v>13.96</v>
+        <v>17.47</v>
       </c>
       <c r="E49" t="n">
-        <v>17.7</v>
+        <v>13.23</v>
       </c>
       <c r="F49" t="n">
-        <v>0.02</v>
+        <v>1.66</v>
       </c>
       <c r="G49" t="n">
-        <v>67.15000000000001</v>
+        <v>3.05</v>
       </c>
       <c r="H49" t="n">
-        <v>0.88</v>
+        <v>0.44</v>
       </c>
       <c r="I49" t="n">
-        <v>2172</v>
+        <v>21623</v>
       </c>
       <c r="J49" t="n">
-        <v>502</v>
+        <v>9027</v>
       </c>
       <c r="K49" t="n">
-        <v>76</v>
+        <v>12</v>
       </c>
       <c r="L49" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M49" t="n">
-        <v>279</v>
+        <v>53689</v>
       </c>
       <c r="N49" t="n">
-        <v>1670</v>
+        <v>12596</v>
       </c>
       <c r="O49" t="n">
-        <v>5.81</v>
+        <v>18.04</v>
       </c>
       <c r="P49" t="n">
-        <v>10.93</v>
-      </c>
-      <c r="Q49" t="inlineStr"/>
+        <v>32.26</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>31.61</v>
+      </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>Siemens Ltd</t>
+          <t xml:space="preserve">Tata Power Company Ltd
+</t>
         </is>
       </c>
       <c r="S49" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
-      <c r="W49" t="inlineStr"/>
+        <v>11.1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1647269.48</v>
+      </c>
+      <c r="U49" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="V49" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0.49</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -9114,75 +10572,75 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>19.82</v>
+        <v>19.14</v>
       </c>
       <c r="D50" t="n">
-        <v>26.84</v>
+        <v>26.69</v>
       </c>
       <c r="E50" t="n">
-        <v>15.09</v>
+        <v>50.94</v>
       </c>
       <c r="F50" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="G50" t="n">
-        <v>58.33</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H50" t="n">
-        <v>0.57</v>
+        <v>1.66</v>
       </c>
       <c r="I50" t="n">
-        <v>12898</v>
+        <v>50429</v>
       </c>
       <c r="J50" t="n">
-        <v>763</v>
+        <v>6091</v>
       </c>
       <c r="K50" t="n">
-        <v>40</v>
+        <v>127</v>
       </c>
       <c r="L50" t="n">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="M50" t="n">
-        <v>3274</v>
+        <v>8021</v>
       </c>
       <c r="N50" t="n">
-        <v>12135</v>
+        <v>44338</v>
       </c>
       <c r="O50" t="n">
-        <v>13.39</v>
+        <v>11.32</v>
       </c>
       <c r="P50" t="n">
-        <v>10.19</v>
+        <v>10.76</v>
       </c>
       <c r="Q50" t="n">
-        <v>10.42</v>
+        <v>11.29</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>Sun Pharmaceuticals Industries Ltd</t>
+          <t>Tata Consultancy Services Ltd</t>
         </is>
       </c>
       <c r="S50" t="n">
-        <v>17.3</v>
+        <v>64.3</v>
       </c>
       <c r="T50" t="n">
-        <v>1339586.09</v>
+        <v>461188.15</v>
       </c>
       <c r="U50" t="n">
-        <v>37.9</v>
+        <v>78.69</v>
       </c>
       <c r="V50" t="n">
-        <v>6.71</v>
+        <v>6.08</v>
       </c>
       <c r="W50" t="n">
-        <v>3.88</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -9191,75 +10649,76 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>7.99</v>
+        <v>6.84</v>
       </c>
       <c r="D51" t="n">
-        <v>15.02</v>
+        <v>10.36</v>
       </c>
       <c r="E51" t="n">
-        <v>7.57</v>
+        <v>37.22</v>
       </c>
       <c r="F51" t="n">
-        <v>0.22</v>
+        <v>1.65</v>
       </c>
       <c r="G51" t="n">
-        <v>25.32</v>
+        <v>9.41</v>
       </c>
       <c r="H51" t="n">
-        <v>0.55</v>
+        <v>1.62</v>
       </c>
       <c r="I51" t="n">
-        <v>3848</v>
+        <v>1884</v>
       </c>
       <c r="J51" t="n">
-        <v>1911</v>
+        <v>189</v>
       </c>
       <c r="K51" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="L51" t="n">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="M51" t="n">
-        <v>3477</v>
+        <v>15528</v>
       </c>
       <c r="N51" t="n">
-        <v>1937</v>
+        <v>1695</v>
       </c>
       <c r="O51" t="n">
-        <v>6.86</v>
+        <v>25.95</v>
       </c>
       <c r="P51" t="n">
-        <v>8.390000000000001</v>
+        <v>35.08</v>
       </c>
       <c r="Q51" t="n">
-        <v>5.95</v>
+        <v>35.43</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>Tata Consumer Products Ltd</t>
+          <t xml:space="preserve">Titan Company Ltd
+</t>
         </is>
       </c>
       <c r="S51" t="n">
-        <v>10.6</v>
+        <v>22.7</v>
       </c>
       <c r="T51" t="n">
-        <v>350543.35</v>
+        <v>1793769.72</v>
       </c>
       <c r="U51" t="n">
-        <v>54.79</v>
+        <v>10.13</v>
       </c>
       <c r="V51" t="n">
-        <v>7.14</v>
+        <v>10.51</v>
       </c>
       <c r="W51" t="n">
-        <v>1.87</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>TATAMOTORS</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -9268,453 +10727,68 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>7.26</v>
+        <v>15.44</v>
       </c>
       <c r="D52" t="n">
-        <v>13.6</v>
+        <v>31.39</v>
       </c>
       <c r="E52" t="n">
-        <v>37.46</v>
+        <v>24.15</v>
       </c>
       <c r="F52" t="n">
-        <v>1.26</v>
+        <v>0.59</v>
       </c>
       <c r="G52" t="n">
-        <v>6.53</v>
+        <v>9.93</v>
       </c>
       <c r="H52" t="n">
-        <v>1.19</v>
+        <v>0.74</v>
       </c>
       <c r="I52" t="n">
-        <v>90697</v>
+        <v>3426</v>
       </c>
       <c r="J52" t="n">
-        <v>22782</v>
+        <v>160</v>
       </c>
       <c r="K52" t="n">
-        <v>94</v>
+        <v>49</v>
       </c>
       <c r="L52" t="n">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="M52" t="n">
-        <v>107262</v>
+        <v>4022</v>
       </c>
       <c r="N52" t="n">
-        <v>67915</v>
+        <v>3266</v>
       </c>
       <c r="O52" t="n">
-        <v>7.31</v>
+        <v>9.01</v>
       </c>
       <c r="P52" t="n">
-        <v>10.71</v>
+        <v>10.43</v>
       </c>
       <c r="Q52" t="n">
-        <v>9.050000000000001</v>
+        <v>10.42</v>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>Tata Motors Ltd</t>
+          <t>Torrent Pharmaceuticals Ltd</t>
         </is>
       </c>
       <c r="S52" t="n">
-        <v>20.1</v>
+        <v>23.2</v>
       </c>
       <c r="T52" t="n">
-        <v>1504106.64</v>
+        <v>1870170.39</v>
       </c>
       <c r="U52" t="n">
-        <v>67.06999999999999</v>
+        <v>46.4</v>
       </c>
       <c r="V52" t="n">
-        <v>0.93</v>
+        <v>6.43</v>
       </c>
       <c r="W52" t="n">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>TATAPOWER</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2024-03</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>6.97</v>
-      </c>
-      <c r="D53" t="n">
-        <v>17.47</v>
-      </c>
-      <c r="E53" t="n">
-        <v>13.23</v>
-      </c>
-      <c r="F53" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="G53" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="I53" t="n">
-        <v>21623</v>
-      </c>
-      <c r="J53" t="n">
-        <v>9027</v>
-      </c>
-      <c r="K53" t="n">
-        <v>12</v>
-      </c>
-      <c r="L53" t="n">
-        <v>17</v>
-      </c>
-      <c r="M53" t="n">
-        <v>53689</v>
-      </c>
-      <c r="N53" t="n">
-        <v>12596</v>
-      </c>
-      <c r="O53" t="n">
-        <v>5.56</v>
-      </c>
-      <c r="P53" t="n">
-        <v>34.74</v>
-      </c>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tata Power Company Ltd
-</t>
-        </is>
-      </c>
-      <c r="S53" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="T53" t="n">
-        <v>1647269.48</v>
-      </c>
-      <c r="U53" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="V53" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="W53" t="n">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>TCS</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2024-03</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>19.14</v>
-      </c>
-      <c r="D54" t="n">
-        <v>26.69</v>
-      </c>
-      <c r="E54" t="n">
-        <v>50.94</v>
-      </c>
-      <c r="F54" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="G54" t="n">
-        <v>87.09999999999999</v>
-      </c>
-      <c r="H54" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="I54" t="n">
-        <v>50429</v>
-      </c>
-      <c r="J54" t="n">
-        <v>6091</v>
-      </c>
-      <c r="K54" t="n">
-        <v>127</v>
-      </c>
-      <c r="L54" t="n">
-        <v>58</v>
-      </c>
-      <c r="M54" t="n">
-        <v>8021</v>
-      </c>
-      <c r="N54" t="n">
-        <v>44338</v>
-      </c>
-      <c r="O54" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="P54" t="n">
-        <v>10.96</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>11.64</v>
-      </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services Ltd</t>
-        </is>
-      </c>
-      <c r="S54" t="n">
-        <v>64.3</v>
-      </c>
-      <c r="T54" t="n">
-        <v>461188.15</v>
-      </c>
-      <c r="U54" t="n">
-        <v>78.69</v>
-      </c>
-      <c r="V54" t="n">
-        <v>6.08</v>
-      </c>
-      <c r="W54" t="n">
-        <v>1.62</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>TECHM</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2024-03</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>4.61</v>
-      </c>
-      <c r="D55" t="n">
-        <v>8.67</v>
-      </c>
-      <c r="E55" t="n">
-        <v>8.99</v>
-      </c>
-      <c r="F55" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G55" t="n">
-        <v>13.86</v>
-      </c>
-      <c r="H55" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="I55" t="n">
-        <v>7694</v>
-      </c>
-      <c r="J55" t="n">
-        <v>1318</v>
-      </c>
-      <c r="K55" t="n">
-        <v>24</v>
-      </c>
-      <c r="L55" t="n">
-        <v>150</v>
-      </c>
-      <c r="M55" t="n">
-        <v>2537</v>
-      </c>
-      <c r="N55" t="n">
-        <v>6376</v>
-      </c>
-      <c r="O55" t="n">
-        <v>18.46</v>
-      </c>
-      <c r="P55" t="n">
-        <v>9.24</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>Tech Mahindra Ltd</t>
-        </is>
-      </c>
-      <c r="S55" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="T55" t="n">
-        <v>3021095.64</v>
-      </c>
-      <c r="U55" t="n">
-        <v>57.4</v>
-      </c>
-      <c r="V55" t="n">
-        <v>7.43</v>
-      </c>
-      <c r="W55" t="n">
-        <v>0.64</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>TITAN</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2024-03</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>6.84</v>
-      </c>
-      <c r="D56" t="n">
-        <v>10.36</v>
-      </c>
-      <c r="E56" t="n">
-        <v>37.22</v>
-      </c>
-      <c r="F56" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="G56" t="n">
-        <v>9.41</v>
-      </c>
-      <c r="H56" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="I56" t="n">
-        <v>1884</v>
-      </c>
-      <c r="J56" t="n">
-        <v>189</v>
-      </c>
-      <c r="K56" t="n">
-        <v>39</v>
-      </c>
-      <c r="L56" t="n">
-        <v>28</v>
-      </c>
-      <c r="M56" t="n">
-        <v>15528</v>
-      </c>
-      <c r="N56" t="n">
-        <v>1695</v>
-      </c>
-      <c r="O56" t="n">
-        <v>15.05</v>
-      </c>
-      <c r="P56" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>13.61</v>
-      </c>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Titan Company Ltd
-</t>
-        </is>
-      </c>
-      <c r="S56" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="T56" t="n">
-        <v>1793769.72</v>
-      </c>
-      <c r="U56" t="n">
-        <v>10.13</v>
-      </c>
-      <c r="V56" t="n">
-        <v>10.51</v>
-      </c>
-      <c r="W56" t="n">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>TORNTPHARM</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2024-03</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>15.44</v>
-      </c>
-      <c r="D57" t="n">
-        <v>31.39</v>
-      </c>
-      <c r="E57" t="n">
-        <v>24.15</v>
-      </c>
-      <c r="F57" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="G57" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I57" t="n">
-        <v>3426</v>
-      </c>
-      <c r="J57" t="n">
-        <v>160</v>
-      </c>
-      <c r="K57" t="n">
-        <v>49</v>
-      </c>
-      <c r="L57" t="n">
-        <v>57</v>
-      </c>
-      <c r="M57" t="n">
-        <v>4022</v>
-      </c>
-      <c r="N57" t="n">
-        <v>3266</v>
-      </c>
-      <c r="O57" t="n">
-        <v>11.08</v>
-      </c>
-      <c r="P57" t="n">
-        <v>12.88</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>12.77</v>
-      </c>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t>Torrent Pharmaceuticals Ltd</t>
-        </is>
-      </c>
-      <c r="S57" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="T57" t="n">
-        <v>1870170.39</v>
-      </c>
-      <c r="U57" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="V57" t="n">
-        <v>6.43</v>
-      </c>
-      <c r="W57" t="n">
         <v>1.22</v>
       </c>
     </row>
